--- a/mag7_gulf_datacenter_exposure.xlsx
+++ b/mag7_gulf_datacenter_exposure.xlsx
@@ -11,12 +11,13 @@
     <sheet name="Summary by Entity" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Summary by Gulf State" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="HUMAIN Ecosystem (Saudi)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Methodology &amp; Notes" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Stargate UAE Ecosystem" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Methodology &amp; Notes" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Project Detail'!$A$1:$Q$41</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Summary by Entity'!$A$1:$L$22</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Summary by Gulf State'!$A$1:$L$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Project Detail'!$A$1:$Q$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Summary by Entity'!$A$1:$L$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Summary by Gulf State'!$A$1:$P$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -25,7 +26,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -40,6 +41,9 @@
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
       <sz val="14"/>
     </font>
     <font>
@@ -47,7 +51,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -92,6 +96,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00BDD7EE"/>
+        <bgColor rgb="00BDD7EE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001D6B3F"/>
+        <bgColor rgb="001D6B3F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00BF4F00"/>
+        <bgColor rgb="00BF4F00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00C55A11"/>
         <bgColor rgb="00C55A11"/>
       </patternFill>
@@ -115,14 +137,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -139,21 +159,33 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -521,26 +553,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q41"/>
+  <dimension ref="A1:Q52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="20" customWidth="1" min="12" max="12"/>
-    <col width="32" customWidth="1" min="13" max="13"/>
-    <col width="50" customWidth="1" min="14" max="14"/>
-    <col width="32" customWidth="1" min="15" max="15"/>
-    <col width="50" customWidth="1" min="16" max="16"/>
-    <col width="65" customWidth="1" min="17" max="17"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="36" customWidth="1" min="13" max="13"/>
+    <col width="52" customWidth="1" min="14" max="14"/>
+    <col width="34" customWidth="1" min="15" max="15"/>
+    <col width="56" customWidth="1" min="16" max="16"/>
+    <col width="68" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -586,17 +618,17 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Live Capacity (GW)</t>
+          <t>Live (GW)</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Planned Capacity (GW)</t>
+          <t>Planned (GW)</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Total Capacity (GW)</t>
+          <t>Total (GW)</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
@@ -606,7 +638,7 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Local Partner</t>
+          <t>Local Partner / Counterparty</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
@@ -707,22 +739,22 @@
       </c>
       <c r="N3" s="4" t="inlineStr">
         <is>
-          <t>Azure cloud (IaaS, PaaS, SaaS); AI/ML inference; Enterprise workloads; Government cloud</t>
+          <t>Azure cloud (IaaS/PaaS/SaaS); AI/ML inference; Enterprise; Government cloud</t>
         </is>
       </c>
       <c r="O3" s="4" t="inlineStr">
         <is>
-          <t>Live (regions since 2019); 200 MW expansion by end-2026</t>
+          <t>Live (since 2019); 200 MW expansion by end-2026</t>
         </is>
       </c>
       <c r="P3" s="4" t="inlineStr">
         <is>
-          <t>Azure UAE North &amp; Central regions; 200 MW Khazna expansion; Availability Zones</t>
+          <t>Azure UAE North &amp; Central; 200 MW Khazna expansion; Availability Zones</t>
         </is>
       </c>
       <c r="Q3" s="4" t="inlineStr">
         <is>
-          <t>Microsoft $15.2B UAE commitment (2023-2029); 200 MW G42/Khazna expansion announced Nov 2025</t>
+          <t>$15.2B UAE (2023-2029); 200 MW G42/Khazna expansion Nov 2025</t>
         </is>
       </c>
     </row>
@@ -744,7 +776,7 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>Eastern Province (Dammam area)</t>
+          <t>Eastern Province</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -778,7 +810,7 @@
       </c>
       <c r="N4" s="4" t="inlineStr">
         <is>
-          <t>Azure cloud (IaaS, PaaS); AI workloads; Sovereign cloud; Enterprise applications</t>
+          <t>Azure cloud; AI workloads; Sovereign cloud; Enterprise</t>
         </is>
       </c>
       <c r="O4" s="4" t="inlineStr">
@@ -788,12 +820,12 @@
       </c>
       <c r="P4" s="4" t="inlineStr">
         <is>
-          <t>3 Azure Availability Zones; construction complete Dec 2024</t>
+          <t>3 Availability Zones; construction complete Dec 2024</t>
         </is>
       </c>
       <c r="Q4" s="4" t="inlineStr">
         <is>
-          <t>Saudi Arabia East datacenter region confirmed for Q4 2026 availability</t>
+          <t>Saudi Arabia East region confirmed Q4 2026</t>
         </is>
       </c>
     </row>
@@ -849,22 +881,22 @@
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
-          <t>Azure cloud; Government workloads; Enterprise applications</t>
+          <t>Azure cloud; Government; Enterprise</t>
         </is>
       </c>
       <c r="O5" s="4" t="inlineStr">
         <is>
-          <t>Live (since ~2022); 10 MW expansion announced 2025</t>
+          <t>Live (~2022); 10 MW expansion 2025</t>
         </is>
       </c>
       <c r="P5" s="4" t="inlineStr">
         <is>
-          <t>Azure Qatar Central region; MEEZA partnership for 4+6 MW expansion</t>
+          <t>Azure Qatar Central; MEEZA 4+6 MW expansion</t>
         </is>
       </c>
       <c r="Q5" s="4" t="inlineStr">
         <is>
-          <t>MCIT-MEEZA cooperation agreement for Azure Qatar expansion at MWC25 Doha</t>
+          <t>MCIT-MEEZA agreement at MWC25 Doha</t>
         </is>
       </c>
     </row>
@@ -912,12 +944,12 @@
       </c>
       <c r="N6" s="4" t="inlineStr">
         <is>
-          <t>Azure cloud; AI transformation; Government workloads</t>
+          <t>Azure cloud; AI transformation</t>
         </is>
       </c>
       <c r="O6" s="4" t="inlineStr">
         <is>
-          <t>TBD (announced intent)</t>
+          <t>TBD (intent announced)</t>
         </is>
       </c>
       <c r="P6" s="4" t="inlineStr">
@@ -927,7 +959,7 @@
       </c>
       <c r="Q6" s="4" t="inlineStr">
         <is>
-          <t>Microsoft announced intent to establish Azure region in Kuwait; no capacity details</t>
+          <t>Announced intent; no capacity details</t>
         </is>
       </c>
     </row>
@@ -949,7 +981,7 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>UAE (Abu Dhabi / Dubai area)</t>
+          <t>Abu Dhabi / Dubai</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
@@ -985,22 +1017,22 @@
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t>AWS cloud (EC2, S3, Lambda, etc.); AI/ML (SageMaker); Enterprise workloads; IoT</t>
+          <t>AWS cloud (EC2, S3, Lambda); AI/ML (SageMaker); Enterprise; IoT</t>
         </is>
       </c>
       <c r="O7" s="4" t="inlineStr">
         <is>
-          <t>Live (since Aug 2022)</t>
+          <t>Live (Aug 2022)</t>
         </is>
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>AWS Middle East (UAE) Region; 3 Availability Zones</t>
+          <t>3 Availability Zones</t>
         </is>
       </c>
       <c r="Q7" s="4" t="inlineStr">
         <is>
-          <t>AWS $5B investment in UAE through 2036; launched Aug 2022</t>
+          <t>$5B UAE investment through 2036; launched Aug 2022</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1054,7 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>Manama area</t>
+          <t>Manama</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
@@ -1056,22 +1088,22 @@
       </c>
       <c r="N8" s="4" t="inlineStr">
         <is>
-          <t>AWS cloud; Enterprise workloads; Government cloud; Financial services</t>
+          <t>AWS cloud; Enterprise; Government; Financial services</t>
         </is>
       </c>
       <c r="O8" s="4" t="inlineStr">
         <is>
-          <t>Live (since Jul 2019)</t>
+          <t>Live (Jul 2019)</t>
         </is>
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>AWS Middle East (Bahrain) Region; 3 Availability Zones</t>
+          <t>3 Availability Zones</t>
         </is>
       </c>
       <c r="Q8" s="4" t="inlineStr">
         <is>
-          <t>First AWS Middle East region; launched July 2019</t>
+          <t>First AWS ME region; July 2019</t>
         </is>
       </c>
     </row>
@@ -1093,7 +1125,7 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Riyadh area</t>
+          <t>Riyadh</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -1124,12 +1156,12 @@
       </c>
       <c r="M9" s="4" t="inlineStr">
         <is>
-          <t>Direct (AWS-owned)</t>
+          <t>Direct / HUMAIN (AI Zone partner)</t>
         </is>
       </c>
       <c r="N9" s="4" t="inlineStr">
         <is>
-          <t>AWS cloud; AI/ML workloads; Enterprise applications; Government cloud</t>
+          <t>AWS cloud; AI/ML; Enterprise; Government; HUMAIN AI Zone</t>
         </is>
       </c>
       <c r="O9" s="4" t="inlineStr">
@@ -1139,12 +1171,12 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>Planned 3 Availability Zones; innovation centers</t>
+          <t>3 Availability Zones; 150,000 AI accelerators via HUMAIN</t>
         </is>
       </c>
       <c r="Q9" s="4" t="inlineStr">
         <is>
-          <t>AWS $5.3B Saudi Arabia investment announced Mar 2024; region planned for 2026</t>
+          <t>$5.3B investment; also HUMAIN preferred AI partner; 150K accelerators</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1198,7 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>Edge Location</t>
+          <t>Edge</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
@@ -1192,7 +1224,7 @@
       </c>
       <c r="N10" s="4" t="inlineStr">
         <is>
-          <t>AWS Local Zone; low-latency edge computing</t>
+          <t>Edge computing; CDN</t>
         </is>
       </c>
       <c r="O10" s="4" t="inlineStr">
@@ -1202,12 +1234,12 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>AWS Local Zone + CloudFront Edge Location</t>
+          <t>Local Zone + CloudFront</t>
         </is>
       </c>
       <c r="Q10" s="4" t="inlineStr">
         <is>
-          <t>AWS Outposts available; Local Zone in Oman; CloudFront edge</t>
+          <t>AWS Outposts + Local Zone + CloudFront</t>
         </is>
       </c>
     </row>
@@ -1229,7 +1261,7 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Edge Location</t>
+          <t>Edge</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
@@ -1255,7 +1287,7 @@
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
-          <t>CloudFront CDN; edge caching</t>
+          <t>CDN; edge caching</t>
         </is>
       </c>
       <c r="O11" s="4" t="inlineStr">
@@ -1265,12 +1297,12 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>CloudFront Edge Location</t>
+          <t>CloudFront Edge</t>
         </is>
       </c>
       <c r="Q11" s="4" t="inlineStr">
         <is>
-          <t>CloudFront edge location in Qatar; AWS Outposts available</t>
+          <t>CloudFront edge; Outposts available</t>
         </is>
       </c>
     </row>
@@ -1328,22 +1360,22 @@
       </c>
       <c r="N12" s="4" t="inlineStr">
         <is>
-          <t>Google Cloud (Compute Engine, GKE, Cloud SQL, Spanner); AI/ML; Data analytics</t>
+          <t>Google Cloud (GCE, GKE, Cloud SQL, Spanner); AI/ML; Analytics</t>
         </is>
       </c>
       <c r="O12" s="4" t="inlineStr">
         <is>
-          <t>Live (since Nov 2023)</t>
+          <t>Live (Nov 2023)</t>
         </is>
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>me-central2 region; 3 Availability Zones</t>
+          <t>me-central2; 3 AZs</t>
         </is>
       </c>
       <c r="Q12" s="4" t="inlineStr">
         <is>
-          <t>Google $1B investment in Dammam; launched Nov 2023</t>
+          <t>$1B Dammam investment; launched Nov 2023</t>
         </is>
       </c>
     </row>
@@ -1399,22 +1431,22 @@
       </c>
       <c r="N13" s="4" t="inlineStr">
         <is>
-          <t>Google Cloud (Compute Engine, Cloud Run, Cloud SQL, GKE, Spanner); AI/ML</t>
+          <t>Google Cloud (GCE, Cloud Run, GKE, Spanner); AI/ML</t>
         </is>
       </c>
       <c r="O13" s="4" t="inlineStr">
         <is>
-          <t>Live (since May 2023)</t>
+          <t>Live (May 2023)</t>
         </is>
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>me-central1 region; 3 Availability Zones</t>
+          <t>me-central1; 3 AZs</t>
         </is>
       </c>
       <c r="Q13" s="4" t="inlineStr">
         <is>
-          <t>Google Cloud Doha region opened May 2023; $18.9B projected economic impact to Qatar by 2030</t>
+          <t>Doha region May 2023; $18.9B projected economic impact by 2030</t>
         </is>
       </c>
     </row>
@@ -1457,12 +1489,12 @@
       <c r="L14" s="4" t="n"/>
       <c r="M14" s="4" t="inlineStr">
         <is>
-          <t>TBD (potentially G42 / Stargate UAE)</t>
+          <t>TBD (G42 / Stargate UAE)</t>
         </is>
       </c>
       <c r="N14" s="4" t="inlineStr">
         <is>
-          <t>Google Cloud; AI/ML inference; Enterprise workloads</t>
+          <t>Google Cloud; AI/ML inference; Enterprise</t>
         </is>
       </c>
       <c r="O14" s="4" t="inlineStr">
@@ -1472,12 +1504,12 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>Evaluating UAE datacenter locations; in discussions for Stargate UAE tenancy</t>
+          <t>Evaluating UAE; Stargate UAE tenancy discussions</t>
         </is>
       </c>
       <c r="Q14" s="4" t="inlineStr">
         <is>
-          <t>Reportedly 'furthest along' in Stargate UAE tenant negotiations alongside Microsoft</t>
+          <t>'Furthest along' in Stargate tenant talks alongside Microsoft</t>
         </is>
       </c>
     </row>
@@ -1525,7 +1557,7 @@
       </c>
       <c r="N15" s="4" t="inlineStr">
         <is>
-          <t>Google Cloud; AI/ML; Enterprise workloads</t>
+          <t>Google Cloud; AI/ML; Enterprise</t>
         </is>
       </c>
       <c r="O15" s="4" t="inlineStr">
@@ -1535,12 +1567,12 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>Planned third GCC cloud region</t>
+          <t>Planned 3rd GCC region</t>
         </is>
       </c>
       <c r="Q15" s="4" t="inlineStr">
         <is>
-          <t>Google Cloud planning Kuwait as third GCC region after Saudi Arabia and Qatar</t>
+          <t>After Saudi and Qatar</t>
         </is>
       </c>
     </row>
@@ -1552,70 +1584,58 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>UAE</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>Various (HUMAIN facilities)</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>Planned (partially live Q1 2026)</t>
+          <t>Abu Dhabi (Stargate UAE tenant talks)</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>Under Discussion</t>
         </is>
       </c>
       <c r="F16" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="G16" s="4" t="n">
-        <v>400</v>
-      </c>
-      <c r="H16" s="4" t="n">
-        <v>500</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G16" s="4" t="n"/>
+      <c r="H16" s="4" t="n"/>
       <c r="I16" s="4" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="J16" s="4" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="K16" s="4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L16" s="4" t="inlineStr">
-        <is>
-          <t>18-24 (GPU procurement)</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J16" s="4" t="n"/>
+      <c r="K16" s="4" t="n"/>
+      <c r="L16" s="4" t="n"/>
       <c r="M16" s="4" t="inlineStr">
         <is>
-          <t>HUMAIN (PIF subsidiary)</t>
+          <t>G42 (potential)</t>
         </is>
       </c>
       <c r="N16" s="4" t="inlineStr">
         <is>
-          <t>AI model training; AI inference; Large-scale GPU computing; Sovereign AI</t>
+          <t>AI training/inference; LLM (Llama)</t>
         </is>
       </c>
       <c r="O16" s="4" t="inlineStr">
         <is>
-          <t>Q2 2026 (first 100 MW); up to 500 MW over 5 years</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>18,000 Nvidia GB300 supercomputers (phase 1); up to 600,000 GPUs over 3 yrs; InfiniBand</t>
+          <t>Potential Stargate UAE tenant</t>
         </is>
       </c>
       <c r="Q16" s="4" t="inlineStr">
         <is>
-          <t>HUMAIN-Nvidia partnership May 2025; first chip shipment Dec 2025; $18-24B GPU deal</t>
+          <t>In discussions; no confirmed capacity</t>
         </is>
       </c>
     </row>
@@ -1627,66 +1647,68 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>UAE</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Abu Dhabi (Stargate UAE)</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>Planned</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t>No Presence</t>
         </is>
       </c>
       <c r="F17" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="I17" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="L17" s="4" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="L17" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="M17" s="4" t="inlineStr">
         <is>
-          <t>G42 / OpenAI / Oracle / SoftBank / Cisco</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N17" s="4" t="inlineStr">
         <is>
-          <t>AI training &amp; inference; GPU-accelerated computing; Large language models</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O17" s="4" t="inlineStr">
         <is>
-          <t>2026 (200 MW phase 1); 5 GW ultimate capacity</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>~100,000 Nvidia GB300 chips (phase 1); part of 5 GW AI campus</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q17" s="4" t="inlineStr">
         <is>
-          <t>Nvidia is infrastructure partner in Stargate UAE consortium; 200 MW first phase 2026</t>
+          <t>No announced Saudi plans</t>
         </is>
       </c>
     </row>
@@ -1698,58 +1720,68 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>UAE</t>
+          <t>All Gulf States</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>Abu Dhabi (Stargate UAE — potential tenant)</t>
-        </is>
-      </c>
-      <c r="E18" s="7" t="inlineStr">
-        <is>
-          <t>Under Discussion</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>No Presence</t>
         </is>
       </c>
       <c r="F18" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G18" s="4" t="n"/>
-      <c r="H18" s="4" t="n"/>
+      <c r="G18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="I18" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="J18" s="4" t="n"/>
-      <c r="K18" s="4" t="n"/>
-      <c r="L18" s="4" t="n"/>
+      <c r="J18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="M18" s="4" t="inlineStr">
         <is>
-          <t>G42 (potential)</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N18" s="4" t="inlineStr">
         <is>
-          <t>AI model training; AI inference; LLM workloads (Llama models)</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O18" s="4" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>Potential tenant at Stargate UAE campus</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q18" s="4" t="inlineStr">
         <is>
-          <t>Meta reportedly in discussions to become tenant at Stargate UAE; no confirmed capacity</t>
+          <t>No DC in any Gulf state; retail expansion only</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1793,12 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>All Gulf States</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -1776,7 +1808,7 @@
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>No Presence</t>
+          <t>No Direct Presence</t>
         </is>
       </c>
       <c r="F19" s="4" t="n">
@@ -1807,193 +1839,191 @@
       </c>
       <c r="N19" s="4" t="inlineStr">
         <is>
+          <t>N/A (see xAI)</t>
+        </is>
+      </c>
+      <c r="O19" s="4" t="inlineStr">
+        <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="O19" s="4" t="inlineStr">
+      <c r="P19" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="P19" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="Q19" s="4" t="inlineStr">
         <is>
-          <t>No announced datacenter plans in Saudi Arabia</t>
+          <t>No direct DC. xAI (Musk's separate co.) has 500 MW Saudi deal</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>Mag7</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>Apple</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>All Gulf States</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E20" s="8" t="inlineStr">
-        <is>
-          <t>No Presence</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N20" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O20" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P20" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q20" s="4" t="inlineStr">
-        <is>
-          <t>No datacenter investments in any Gulf state; retail expansion only (Saudi stores from 2026)</t>
-        </is>
-      </c>
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>AI LABS (OpenAI, Anthropic, xAI)</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="inlineStr"/>
+      <c r="C20" s="10" t="inlineStr"/>
+      <c r="D20" s="10" t="inlineStr"/>
+      <c r="E20" s="10" t="inlineStr"/>
+      <c r="F20" s="10" t="inlineStr"/>
+      <c r="G20" s="10" t="inlineStr"/>
+      <c r="H20" s="10" t="inlineStr"/>
+      <c r="I20" s="10" t="inlineStr"/>
+      <c r="J20" s="10" t="inlineStr"/>
+      <c r="K20" s="10" t="inlineStr"/>
+      <c r="L20" s="10" t="inlineStr"/>
+      <c r="M20" s="10" t="inlineStr"/>
+      <c r="N20" s="10" t="inlineStr"/>
+      <c r="O20" s="10" t="inlineStr"/>
+      <c r="P20" s="10" t="inlineStr"/>
+      <c r="Q20" s="10" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Mag7</t>
+          <t>AI Lab</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>All Gulf States</t>
+          <t>UAE</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
+          <t>Abu Dhabi (Stargate UAE)</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H21" s="4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L21" s="4" t="n"/>
+      <c r="M21" s="4" t="inlineStr">
+        <is>
+          <t>G42 / Oracle / SoftBank / Nvidia / Cisco</t>
+        </is>
+      </c>
+      <c r="N21" s="4" t="inlineStr">
+        <is>
+          <t>AI training &amp; inference (GPT); OpenAI for Countries</t>
+        </is>
+      </c>
+      <c r="O21" s="4" t="inlineStr">
+        <is>
+          <t>Q3 2026 (200 MW); 1 GW in ~3 yrs</t>
+        </is>
+      </c>
+      <c r="P21" s="4" t="inlineStr">
+        <is>
+          <t>Nvidia GB300; ~100K chips ph1; 10 sq mi campus (5 GW ultimate)</t>
+        </is>
+      </c>
+      <c r="Q21" s="4" t="inlineStr">
+        <is>
+          <t>Stargate UAE May 2025; first intl Stargate; &gt;$30B total cost</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>AI Lab</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="E21" s="8" t="inlineStr">
+      <c r="E22" s="8" t="inlineStr">
         <is>
           <t>No Direct Presence</t>
         </is>
       </c>
-      <c r="F21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" s="4" t="inlineStr">
+      <c r="F22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="N21" s="4" t="inlineStr">
-        <is>
-          <t>N/A (see xAI note)</t>
-        </is>
-      </c>
-      <c r="O21" s="4" t="inlineStr">
+      <c r="N22" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="P21" s="4" t="inlineStr">
+      <c r="O22" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="Q21" s="4" t="inlineStr">
-        <is>
-          <t>No direct datacenter presence. xAI (Musk's separate company) has 500 MW deal w/ HUMAIN in Saudi Arabia</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="9" t="inlineStr">
-        <is>
-          <t>AI LABS (OpenAI, Anthropic, xAI)</t>
-        </is>
-      </c>
-      <c r="B22" s="10" t="inlineStr"/>
-      <c r="C22" s="10" t="inlineStr"/>
-      <c r="D22" s="10" t="inlineStr"/>
-      <c r="E22" s="10" t="inlineStr"/>
-      <c r="F22" s="10" t="inlineStr"/>
-      <c r="G22" s="10" t="inlineStr"/>
-      <c r="H22" s="10" t="inlineStr"/>
-      <c r="I22" s="10" t="inlineStr"/>
-      <c r="J22" s="10" t="inlineStr"/>
-      <c r="K22" s="10" t="inlineStr"/>
-      <c r="L22" s="10" t="inlineStr"/>
-      <c r="M22" s="10" t="inlineStr"/>
-      <c r="N22" s="10" t="inlineStr"/>
-      <c r="O22" s="10" t="inlineStr"/>
-      <c r="P22" s="10" t="inlineStr"/>
-      <c r="Q22" s="10" t="inlineStr"/>
+      <c r="P22" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q22" s="4" t="inlineStr">
+        <is>
+          <t>In talks w/ HUMAIN re: VC fund; no infra commitment</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
@@ -2003,7 +2033,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -2013,56 +2043,58 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>Abu Dhabi (Stargate UAE)</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>Planned</t>
+          <t>Via AWS cross-region</t>
+        </is>
+      </c>
+      <c r="E23" s="11" t="inlineStr">
+        <is>
+          <t>Indirect (via AWS)</t>
         </is>
       </c>
       <c r="F23" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="I23" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L23" s="4" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="L23" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="M23" s="4" t="inlineStr">
         <is>
-          <t>G42 / Oracle / SoftBank / Nvidia / Cisco</t>
+          <t>Amazon (AWS)</t>
         </is>
       </c>
       <c r="N23" s="4" t="inlineStr">
         <is>
-          <t>AI model training &amp; inference; LLM workloads (GPT); OpenAI for Countries initiative</t>
+          <t>Claude inference via Amazon Bedrock cross-region</t>
         </is>
       </c>
       <c r="O23" s="4" t="inlineStr">
         <is>
-          <t>Q3 2026 (first 200 MW); full 1 GW within 3 years</t>
+          <t>Available now</t>
         </is>
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>Nvidia GB300 systems; ~100,000 chips phase 1; ~1,400 servers; 10 sq mi campus (5 GW ultimate)</t>
+          <t>Bedrock cross-region inference</t>
         </is>
       </c>
       <c r="Q23" s="4" t="inlineStr">
         <is>
-          <t>Stargate UAE announced May 2025; first international Stargate deployment; OpenAI for Countries initiative</t>
+          <t>Claude models in UAE via AWS; no owned infra</t>
         </is>
       </c>
     </row>
@@ -2074,22 +2106,22 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>Bahrain</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E24" s="8" t="inlineStr">
-        <is>
-          <t>No Direct Presence</t>
+          <t>Via AWS cross-region</t>
+        </is>
+      </c>
+      <c r="E24" s="11" t="inlineStr">
+        <is>
+          <t>Indirect (via AWS)</t>
         </is>
       </c>
       <c r="F24" s="4" t="n">
@@ -2115,27 +2147,27 @@
       </c>
       <c r="M24" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Amazon (AWS)</t>
         </is>
       </c>
       <c r="N24" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Claude inference via Amazon Bedrock</t>
         </is>
       </c>
       <c r="O24" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Available now</t>
         </is>
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Bedrock cross-region inference</t>
         </is>
       </c>
       <c r="Q24" s="4" t="inlineStr">
         <is>
-          <t>No announced Saudi datacenter. In talks with HUMAIN re: $10B VC fund but no infra commitment</t>
+          <t>Claude in Bahrain via AWS; $50B DC plan is US-only</t>
         </is>
       </c>
     </row>
@@ -2147,68 +2179,66 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>xAI (Elon Musk)</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>UAE</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>Via AWS cross-region inference</t>
-        </is>
-      </c>
-      <c r="E25" s="8" t="inlineStr">
-        <is>
-          <t>Indirect (via AWS)</t>
+          <t>HUMAIN facilities</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>Planned</t>
         </is>
       </c>
       <c r="F25" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="I25" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" s="4" t="n">
-        <v>0</v>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L25" s="4" t="n"/>
       <c r="M25" s="4" t="inlineStr">
         <is>
-          <t>Amazon (AWS)</t>
+          <t>HUMAIN (PIF subsidiary)</t>
         </is>
       </c>
       <c r="N25" s="4" t="inlineStr">
         <is>
-          <t>Claude model inference via Amazon Bedrock cross-region; no dedicated local capacity</t>
+          <t>AI training (Grok); AI inference; GPU computing</t>
         </is>
       </c>
       <c r="O25" s="4" t="inlineStr">
         <is>
-          <t>Available now (via AWS UAE region)</t>
+          <t>2026-27 (phased)</t>
         </is>
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>Amazon Bedrock cross-region inference; Claude Opus/Sonnet/Haiku models available</t>
+          <t>500 MW; Nvidia GB300 GPUs; Grok deployment</t>
         </is>
       </c>
       <c r="Q25" s="4" t="inlineStr">
         <is>
-          <t>Claude available in UAE &amp; Bahrain via AWS Bedrock; no Anthropic-owned Gulf infrastructure</t>
+          <t>xAI-HUMAIN Nov 2025; Grok to deploy nationwide</t>
         </is>
       </c>
     </row>
@@ -2220,224 +2250,152 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>xAI (Elon Musk)</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>Bahrain</t>
+          <t>UAE</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>Via AWS cross-region inference</t>
-        </is>
-      </c>
-      <c r="E26" s="8" t="inlineStr">
-        <is>
-          <t>Indirect (via AWS)</t>
+          <t>Abu Dhabi (Stargate tenant talks)</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>Under Discussion</t>
         </is>
       </c>
       <c r="F26" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G26" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="G26" s="4" t="n"/>
+      <c r="H26" s="4" t="n"/>
       <c r="I26" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="J26" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="J26" s="4" t="n"/>
+      <c r="K26" s="4" t="n"/>
+      <c r="L26" s="4" t="n"/>
       <c r="M26" s="4" t="inlineStr">
         <is>
-          <t>Amazon (AWS)</t>
+          <t>G42</t>
         </is>
       </c>
       <c r="N26" s="4" t="inlineStr">
         <is>
-          <t>Claude model inference via Amazon Bedrock cross-region</t>
+          <t>AI training/inference (Grok)</t>
         </is>
       </c>
       <c r="O26" s="4" t="inlineStr">
         <is>
-          <t>Available now (via AWS Bahrain region)</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>Amazon Bedrock cross-region inference</t>
+          <t>Potential Stargate UAE tenant</t>
         </is>
       </c>
       <c r="Q26" s="4" t="inlineStr">
         <is>
-          <t>Claude models accessible via AWS Middle East (Bahrain) region; no dedicated infra</t>
+          <t>In discussions</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>AI Lab</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>Anthropic</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>All Other Gulf States</t>
-        </is>
-      </c>
-      <c r="D27" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E27" s="8" t="inlineStr">
-        <is>
-          <t>No Presence</t>
-        </is>
-      </c>
-      <c r="F27" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N27" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O27" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P27" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q27" s="4" t="inlineStr">
-        <is>
-          <t>Anthropic's $50B datacenter plan focuses on US (Texas, New York). No Gulf-specific plans announced</t>
-        </is>
-      </c>
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>SOVEREIGN WEALTH FUNDS &amp; STATE ENTITIES (Mubadala, G42, HUMAIN, MGX)</t>
+        </is>
+      </c>
+      <c r="B27" s="13" t="inlineStr"/>
+      <c r="C27" s="13" t="inlineStr"/>
+      <c r="D27" s="13" t="inlineStr"/>
+      <c r="E27" s="13" t="inlineStr"/>
+      <c r="F27" s="13" t="inlineStr"/>
+      <c r="G27" s="13" t="inlineStr"/>
+      <c r="H27" s="13" t="inlineStr"/>
+      <c r="I27" s="13" t="inlineStr"/>
+      <c r="J27" s="13" t="inlineStr"/>
+      <c r="K27" s="13" t="inlineStr"/>
+      <c r="L27" s="13" t="inlineStr"/>
+      <c r="M27" s="13" t="inlineStr"/>
+      <c r="N27" s="13" t="inlineStr"/>
+      <c r="O27" s="13" t="inlineStr"/>
+      <c r="P27" s="13" t="inlineStr"/>
+      <c r="Q27" s="13" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>AI Lab</t>
+          <t>Sovereign Wealth / State</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>xAI (Elon Musk)</t>
+          <t>Mubadala</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>UAE</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>Various (HUMAIN facilities)</t>
-        </is>
-      </c>
-      <c r="E28" s="5" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="F28" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" s="4" t="n">
-        <v>500</v>
-      </c>
-      <c r="H28" s="4" t="n">
-        <v>500</v>
-      </c>
-      <c r="I28" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" s="4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K28" s="4" t="n">
-        <v>0.5</v>
-      </c>
+          <t>Abu Dhabi</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>Live (via G42 + portfolio)</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="n"/>
+      <c r="G28" s="4" t="n"/>
+      <c r="H28" s="4" t="n"/>
+      <c r="I28" s="4" t="n"/>
+      <c r="J28" s="4" t="n"/>
+      <c r="K28" s="4" t="n"/>
       <c r="L28" s="4" t="n"/>
       <c r="M28" s="4" t="inlineStr">
         <is>
-          <t>HUMAIN (PIF subsidiary)</t>
+          <t>G42 (backer); GlobalFoundries (81% owner)</t>
         </is>
       </c>
       <c r="N28" s="4" t="inlineStr">
         <is>
-          <t>AI model training (Grok); AI inference; GPU computing</t>
+          <t>Sovereign wealth backing for G42/Khazna DC ecosystem; semiconductor supply via GlobalFoundries</t>
         </is>
       </c>
       <c r="O28" s="4" t="inlineStr">
         <is>
-          <t>2026-2027 (phased deployment)</t>
+          <t>Ongoing</t>
         </is>
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>500 MW flagship facility; Nvidia GB300 GPUs; Grok model deployment</t>
+          <t>Majority shareholder G42; 81% stake in GlobalFoundries ($16B US chip expansion)</t>
         </is>
       </c>
       <c r="Q28" s="4" t="inlineStr">
         <is>
-          <t>xAI-HUMAIN partnership announced Nov 2025; 500 MW datacenter; Grok to be deployed in Saudi Arabia</t>
+          <t>G42 backer alongside Microsoft, Silver Lake. GlobalFoundries $16B semi expansion. $1.4T US infra pledge over 10 yrs</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>AI Lab</t>
+          <t>Sovereign Wealth / State</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>xAI (Elon Musk)</t>
+          <t>Mubadala</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -2447,12 +2405,12 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>Abu Dhabi (Stargate UAE — potential tenant)</t>
-        </is>
-      </c>
-      <c r="E29" s="7" t="inlineStr">
-        <is>
-          <t>Under Discussion</t>
+          <t>Abu Dhabi (Stargate UAE — indirect)</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>Planned (indirect via G42)</t>
         </is>
       </c>
       <c r="F29" s="4" t="n">
@@ -2468,135 +2426,173 @@
       <c r="L29" s="4" t="n"/>
       <c r="M29" s="4" t="inlineStr">
         <is>
+          <t>G42 / Khazna / MGX</t>
+        </is>
+      </c>
+      <c r="N29" s="4" t="inlineStr">
+        <is>
+          <t>AI infrastructure via G42 ecosystem; Stargate UAE campus</t>
+        </is>
+      </c>
+      <c r="O29" s="4" t="inlineStr">
+        <is>
+          <t>2026+</t>
+        </is>
+      </c>
+      <c r="P29" s="4" t="inlineStr">
+        <is>
+          <t>Indirect via G42 → Khazna → Stargate UAE; also founding partner of MGX</t>
+        </is>
+      </c>
+      <c r="Q29" s="4" t="inlineStr">
+        <is>
+          <t>Mubadala is founding partner of MGX and backer of G42; indirect Stargate exposure</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Sovereign Wealth / State</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
           <t>G42</t>
         </is>
       </c>
-      <c r="N29" s="4" t="inlineStr">
-        <is>
-          <t>AI model training &amp; inference (Grok)</t>
-        </is>
-      </c>
-      <c r="O29" s="4" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="P29" s="4" t="inlineStr">
-        <is>
-          <t>Potential tenant at Stargate UAE</t>
-        </is>
-      </c>
-      <c r="Q29" s="4" t="inlineStr">
-        <is>
-          <t>xAI reportedly in discussions to become tenant at Stargate UAE</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="11" t="inlineStr">
-        <is>
-          <t>PRIVATE EQUITY &amp; FINANCIAL SPONSORS</t>
-        </is>
-      </c>
-      <c r="B30" s="12" t="inlineStr"/>
-      <c r="C30" s="12" t="inlineStr"/>
-      <c r="D30" s="12" t="inlineStr"/>
-      <c r="E30" s="12" t="inlineStr"/>
-      <c r="F30" s="12" t="inlineStr"/>
-      <c r="G30" s="12" t="inlineStr"/>
-      <c r="H30" s="12" t="inlineStr"/>
-      <c r="I30" s="12" t="inlineStr"/>
-      <c r="J30" s="12" t="inlineStr"/>
-      <c r="K30" s="12" t="inlineStr"/>
-      <c r="L30" s="12" t="inlineStr"/>
-      <c r="M30" s="12" t="inlineStr"/>
-      <c r="N30" s="12" t="inlineStr"/>
-      <c r="O30" s="12" t="inlineStr"/>
-      <c r="P30" s="12" t="inlineStr"/>
-      <c r="Q30" s="12" t="inlineStr"/>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>Abu Dhabi / Dubai</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>Live + Expanding</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="n">
+        <v>263</v>
+      </c>
+      <c r="G30" s="4" t="n">
+        <v>937</v>
+      </c>
+      <c r="H30" s="4" t="n">
+        <v>1200</v>
+      </c>
+      <c r="I30" s="4" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="J30" s="4" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="K30" s="4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L30" s="4" t="n"/>
+      <c r="M30" s="4" t="inlineStr">
+        <is>
+          <t>Khazna Data Centers (subsidiary); Core42 (AI cloud subsidiary)</t>
+        </is>
+      </c>
+      <c r="N30" s="4" t="inlineStr">
+        <is>
+          <t>Hyperscale DC (Khazna); AI cloud (Core42); Stargate UAE developer; Microsoft Azure partner</t>
+        </is>
+      </c>
+      <c r="O30" s="4" t="inlineStr">
+        <is>
+          <t>263 MW live; Stargate 200 MW Q3 2026; 1 GW+ expanding</t>
+        </is>
+      </c>
+      <c r="P30" s="4" t="inlineStr">
+        <is>
+          <t>Khazna: 30 DCs, 263 MW live, 175 MW building; Stargate UAE 1 GW (5 GW ultimate); Nvidia GB300 certified</t>
+        </is>
+      </c>
+      <c r="Q30" s="4" t="inlineStr">
+        <is>
+          <t>G42 is developer of Stargate UAE; Khazna valued ~$5.5B; Core42 sovereign cloud; backed by Mubadala, Microsoft, Silver Lake</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>PE / Financial</t>
+          <t>Sovereign Wealth / State</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>KKR</t>
+          <t>G42</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>UAE</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>Dubai (+ expansion)</t>
+          <t>Planned (Khazna expansion)</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>Live + Expanding</t>
+          <t>Planned</t>
         </is>
       </c>
       <c r="F31" s="4" t="n">
-        <v>150</v>
-      </c>
-      <c r="G31" s="4" t="n">
-        <v>350</v>
-      </c>
-      <c r="H31" s="4" t="n">
-        <v>500</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G31" s="4" t="n"/>
+      <c r="H31" s="4" t="n"/>
       <c r="I31" s="4" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="J31" s="4" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="K31" s="4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L31" s="4" t="n">
-        <v>5</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J31" s="4" t="n"/>
+      <c r="K31" s="4" t="n"/>
+      <c r="L31" s="4" t="n"/>
       <c r="M31" s="4" t="inlineStr">
         <is>
-          <t>Gulf Data Hub</t>
+          <t>Direct (Khazna)</t>
         </is>
       </c>
       <c r="N31" s="4" t="inlineStr">
         <is>
-          <t>Colocation; Hyperscale; Cloud; AI-ready infrastructure</t>
+          <t>Hyperscale; AI-ready colocation</t>
         </is>
       </c>
       <c r="O31" s="4" t="inlineStr">
         <is>
-          <t>7 DCs live; expansion across GCC ongoing</t>
+          <t>TBD (targeting 25% market share by 2030)</t>
         </is>
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>Gulf Data Hub operates 7 DCs in UAE &amp; Saudi; expanding to Kuwait, Qatar, Bahrain, Oman</t>
+          <t>Khazna targeting 2+ GW Saudi capacity</t>
         </is>
       </c>
       <c r="Q31" s="4" t="inlineStr">
         <is>
-          <t>KKR acquired stake in Gulf Data Hub Jan 2025; $5B+ total investment commitment</t>
+          <t>Khazna Saudi expansion; 25% market share target by 2030</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>PE / Financial</t>
+          <t>Sovereign Wealth / State</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>KKR</t>
+          <t>HUMAIN (PIF)</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -2606,196 +2602,160 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>Various (Gulf Data Hub)</t>
+          <t>Riyadh / Dammam / various</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>Live + Expanding</t>
-        </is>
-      </c>
-      <c r="F32" s="4" t="n"/>
-      <c r="G32" s="4" t="n"/>
-      <c r="H32" s="4" t="n"/>
-      <c r="I32" s="4" t="n"/>
-      <c r="J32" s="4" t="n"/>
-      <c r="K32" s="4" t="n"/>
-      <c r="L32" s="4" t="n"/>
+          <t>Planned (partially live early 2026)</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="G32" s="4" t="n">
+        <v>1800</v>
+      </c>
+      <c r="H32" s="4" t="n">
+        <v>1900</v>
+      </c>
+      <c r="I32" s="4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J32" s="4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="K32" s="4" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="L32" s="4" t="n">
+        <v>77</v>
+      </c>
       <c r="M32" s="4" t="inlineStr">
         <is>
-          <t>Gulf Data Hub</t>
+          <t>Multiple: Nvidia, AMD, Cisco, xAI, AirTrunk, AWS, STC, Luma AI</t>
         </is>
       </c>
       <c r="N32" s="4" t="inlineStr">
         <is>
-          <t>Colocation; Hyperscale; Enterprise</t>
+          <t>National AI platform; sovereign AI; AI training &amp; inference; GPU computing</t>
         </is>
       </c>
       <c r="O32" s="4" t="inlineStr">
         <is>
-          <t>Existing + expansion</t>
+          <t>100 MW Q2 2026 → 1.9 GW by 2030 → 6.6 GW by 2034</t>
         </is>
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>Part of Gulf Data Hub GCC-wide platform</t>
+          <t>Nvidia 500 MW (18K GB300s); AMD/Cisco 1 GW JV; xAI 500 MW; AirTrunk $3B campus; STC 1 GW JV; AWS 150K accelerators</t>
         </is>
       </c>
       <c r="Q32" s="4" t="inlineStr">
         <is>
-          <t>Gulf Data Hub has existing Saudi operations; expansion planned under KKR partnership</t>
+          <t>HUMAIN est. 2025 by PIF; $77B total infra est.; $10B VC fund; targeting 7% global AI compute by 2030</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>PE / Financial</t>
+          <t>Sovereign Wealth / State</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Blackstone (via AirTrunk)</t>
+          <t>MGX</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>UAE</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>TBD (HUMAIN campus)</t>
+          <t>Abu Dhabi</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Live (via Khazna) + Expanding</t>
         </is>
       </c>
       <c r="F33" s="4" t="n">
-        <v>0</v>
+        <v>263</v>
       </c>
       <c r="G33" s="4" t="n"/>
       <c r="H33" s="4" t="n"/>
       <c r="I33" s="4" t="n">
-        <v>0</v>
+        <v>0.26</v>
       </c>
       <c r="J33" s="4" t="n"/>
       <c r="K33" s="4" t="n"/>
-      <c r="L33" s="4" t="n">
-        <v>3</v>
+      <c r="L33" s="4" t="inlineStr">
+        <is>
+          <t>~5.5 (Khazna valuation)</t>
+        </is>
       </c>
       <c r="M33" s="4" t="inlineStr">
         <is>
-          <t>HUMAIN (PIF subsidiary) / AirTrunk</t>
+          <t>Khazna Data Centers (minority stake); G42</t>
         </is>
       </c>
       <c r="N33" s="4" t="inlineStr">
         <is>
-          <t>Hyperscale AI-ready datacenter; AI training &amp; inference</t>
+          <t>AI infrastructure investment; DC portfolio management; Stargate UAE support</t>
         </is>
       </c>
       <c r="O33" s="4" t="inlineStr">
         <is>
-          <t>2026 (initial phase)</t>
+          <t>Khazna 263 MW live; ongoing expansion</t>
         </is>
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>Large-scale DC campus; AirTrunk's first Middle East project</t>
+          <t>Minority stake in Khazna; founding partner of AIP ($30-100B) with BlackRock, Microsoft, Nvidia</t>
         </is>
       </c>
       <c r="Q33" s="4" t="inlineStr">
         <is>
-          <t>HUMAIN-AirTrunk $3B partnership announced Oct 2025; HUMAIN targeting 1.9 GW by 2030</t>
+          <t>MGX est. Mar 2024; $100B AI fund; Khazna stake Mar 2025; Aligned DC $40B acq; $30B AIP with BlackRock; Paris 1.4 GW campus</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>PE / Financial</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>Silver Lake + MGX</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="inlineStr">
-        <is>
-          <t>UAE</t>
-        </is>
-      </c>
-      <c r="D34" s="4" t="inlineStr">
-        <is>
-          <t>Abu Dhabi / Dubai (Khazna facilities)</t>
-        </is>
-      </c>
-      <c r="E34" s="5" t="inlineStr">
-        <is>
-          <t>Live + Expanding</t>
-        </is>
-      </c>
-      <c r="F34" s="4" t="n">
-        <v>263</v>
-      </c>
-      <c r="G34" s="4" t="n">
-        <v>175</v>
-      </c>
-      <c r="H34" s="4" t="n">
-        <v>438</v>
-      </c>
-      <c r="I34" s="4" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="J34" s="4" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="K34" s="4" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="L34" s="4" t="inlineStr">
-        <is>
-          <t>~5.5 (valuation)</t>
-        </is>
-      </c>
-      <c r="M34" s="4" t="inlineStr">
-        <is>
-          <t>Khazna Data Centers (G42 subsidiary)</t>
-        </is>
-      </c>
-      <c r="N34" s="4" t="inlineStr">
-        <is>
-          <t>Wholesale colocation; Hyperscale; AI-ready; Cloud infrastructure</t>
-        </is>
-      </c>
-      <c r="O34" s="4" t="inlineStr">
-        <is>
-          <t>263 MW live; 175 MW under development</t>
-        </is>
-      </c>
-      <c r="P34" s="4" t="inlineStr">
-        <is>
-          <t>Khazna operates 360 MW globally; 263 MW computing active; valued at ~$5.5B</t>
-        </is>
-      </c>
-      <c r="Q34" s="4" t="inlineStr">
-        <is>
-          <t>Silver Lake &amp; MGX acquired minority stakes in Khazna Mar 2025 (e&amp; $2.2B exit)</t>
-        </is>
-      </c>
+      <c r="A34" s="14" t="inlineStr">
+        <is>
+          <t>TECHNOLOGY &amp; INFRASTRUCTURE PARTNERS (Nvidia, AMD, Oracle, Cisco, SoftBank)</t>
+        </is>
+      </c>
+      <c r="B34" s="15" t="inlineStr"/>
+      <c r="C34" s="15" t="inlineStr"/>
+      <c r="D34" s="15" t="inlineStr"/>
+      <c r="E34" s="15" t="inlineStr"/>
+      <c r="F34" s="15" t="inlineStr"/>
+      <c r="G34" s="15" t="inlineStr"/>
+      <c r="H34" s="15" t="inlineStr"/>
+      <c r="I34" s="15" t="inlineStr"/>
+      <c r="J34" s="15" t="inlineStr"/>
+      <c r="K34" s="15" t="inlineStr"/>
+      <c r="L34" s="15" t="inlineStr"/>
+      <c r="M34" s="15" t="inlineStr"/>
+      <c r="N34" s="15" t="inlineStr"/>
+      <c r="O34" s="15" t="inlineStr"/>
+      <c r="P34" s="15" t="inlineStr"/>
+      <c r="Q34" s="15" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>PE / Financial</t>
+          <t>Technology / Infrastructure</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Silver Lake + MGX</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -2805,70 +2765,82 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>Planned (Khazna expansion)</t>
+          <t>Various (HUMAIN facilities)</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Planned (partially live Q1 2026)</t>
         </is>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G35" s="4" t="n"/>
-      <c r="H35" s="4" t="n"/>
+        <v>100</v>
+      </c>
+      <c r="G35" s="4" t="n">
+        <v>400</v>
+      </c>
+      <c r="H35" s="4" t="n">
+        <v>500</v>
+      </c>
       <c r="I35" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" s="4" t="n"/>
-      <c r="K35" s="4" t="n"/>
-      <c r="L35" s="4" t="n"/>
+        <v>0.1</v>
+      </c>
+      <c r="J35" s="4" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K35" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L35" s="4" t="inlineStr">
+        <is>
+          <t>18-24 (GPU procurement)</t>
+        </is>
+      </c>
       <c r="M35" s="4" t="inlineStr">
         <is>
-          <t>Khazna Data Centers</t>
+          <t>HUMAIN (PIF subsidiary)</t>
         </is>
       </c>
       <c r="N35" s="4" t="inlineStr">
         <is>
-          <t>Hyperscale; AI; Wholesale colocation</t>
+          <t>AI training; AI inference; GPU computing; Sovereign AI factories</t>
         </is>
       </c>
       <c r="O35" s="4" t="inlineStr">
         <is>
-          <t>Targeting 25% Saudi market share by 2030</t>
+          <t>Q2 2026 (100 MW); 500 MW over 5 yrs</t>
         </is>
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>Plans for 2+ GW computing capacity in Saudi Arabia</t>
+          <t>18,000 GB300 supercomputers ph1; up to 600K GPUs over 3 yrs; InfiniBand; Omniverse</t>
         </is>
       </c>
       <c r="Q35" s="4" t="inlineStr">
         <is>
-          <t>Khazna targeting 2+ GW Saudi capacity; 25% market share by 2030</t>
+          <t>HUMAIN-Nvidia May 2025; first chip shipment Dec 2025; $18-24B GPU deal</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>PE / Financial</t>
+          <t>Technology / Infrastructure</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>Brookfield</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Qatar</t>
+          <t>UAE</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Abu Dhabi (Stargate UAE + Khazna)</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -2879,51 +2851,57 @@
       <c r="F36" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G36" s="4" t="n"/>
-      <c r="H36" s="4" t="n"/>
+      <c r="G36" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="H36" s="4" t="n">
+        <v>200</v>
+      </c>
       <c r="I36" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="J36" s="4" t="n"/>
-      <c r="K36" s="4" t="n"/>
-      <c r="L36" s="4" t="n">
-        <v>20</v>
-      </c>
+      <c r="J36" s="4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="K36" s="4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L36" s="4" t="n"/>
       <c r="M36" s="4" t="inlineStr">
         <is>
-          <t>Qai (Qatar AI platform) / QIA</t>
+          <t>G42 / Khazna / OpenAI / Oracle / SoftBank / Cisco</t>
         </is>
       </c>
       <c r="N36" s="4" t="inlineStr">
         <is>
-          <t>AI infrastructure; High-performance compute; Data handling</t>
+          <t>AI training &amp; inference; GPU-accelerated computing; LLMs</t>
         </is>
       </c>
       <c r="O36" s="4" t="inlineStr">
         <is>
-          <t>TBD (JV established Dec 2025)</t>
+          <t>Q3 2026 (200 MW ph1); 5 GW ultimate</t>
         </is>
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>$20B JV with Qatar's Qai; backed by Government of Qatar and QIA</t>
+          <t>~100K GB300 chips ph1; Khazna Blackwell-certified designs; up to 250 MW per cluster</t>
         </is>
       </c>
       <c r="Q36" s="4" t="inlineStr">
         <is>
-          <t>Brookfield-Qai $20B AI infrastructure JV announced Dec 2025; Qatar and select international projects</t>
+          <t>Stargate UAE partner; Khazna collaboration for MEA-wide Blackwell deployment</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>PE / Financial</t>
+          <t>Technology / Infrastructure</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Brookfield</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -2933,7 +2911,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>Various</t>
+          <t>Various (HUMAIN / JV facilities)</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -2944,49 +2922,59 @@
       <c r="F37" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G37" s="4" t="n"/>
-      <c r="H37" s="4" t="n"/>
+      <c r="G37" s="4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H37" s="4" t="n">
+        <v>1000</v>
+      </c>
       <c r="I37" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="J37" s="4" t="n"/>
-      <c r="K37" s="4" t="n"/>
-      <c r="L37" s="4" t="n"/>
+      <c r="J37" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K37" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L37" s="4" t="n">
+        <v>10</v>
+      </c>
       <c r="M37" s="4" t="inlineStr">
         <is>
-          <t>Ori Industries (acquired by Brookfield)</t>
+          <t>HUMAIN (PIF) / Cisco (JV partner)</t>
         </is>
       </c>
       <c r="N37" s="4" t="inlineStr">
         <is>
-          <t>AI cloud; Edge computing; Distributed AI workloads</t>
+          <t>AI training &amp; inference; GPU computing (Instinct MI450); CPU (EPYC); Edge (Ryzen AI)</t>
         </is>
       </c>
       <c r="O37" s="4" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>2026 (100 MW ph1); 1 GW by 2030</t>
         </is>
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>Acquired Ori Industries (Saudi Aramco Wa'ed-backed); merged into Radiant Infrastructure</t>
+          <t>AMD/Cisco/HUMAIN JV; Instinct MI450 GPUs; EPYC CPUs; Pensando DPUs; ROCm; Center of Excellence</t>
         </is>
       </c>
       <c r="Q37" s="4" t="inlineStr">
         <is>
-          <t>Brookfield acquired Ori Industries for Saudi AI/edge computing; part of $100B AI infra fund</t>
+          <t>$10B AMD-HUMAIN collaboration May 2025; AMD/Cisco/HUMAIN JV Nov 2025; Luma AI 1st customer (100 MW)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>PE / Financial</t>
+          <t>Technology / Infrastructure</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>DigitalBridge</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -2996,60 +2984,58 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Jeddah / Riyadh / NEOM (planned)</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="F38" s="4" t="n">
-        <v>0</v>
-      </c>
+          <t>Live + Expanding</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="n"/>
       <c r="G38" s="4" t="n"/>
       <c r="H38" s="4" t="n"/>
-      <c r="I38" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="I38" s="4" t="n"/>
       <c r="J38" s="4" t="n"/>
       <c r="K38" s="4" t="n"/>
-      <c r="L38" s="4" t="n"/>
+      <c r="L38" s="4" t="n">
+        <v>1.5</v>
+      </c>
       <c r="M38" s="4" t="inlineStr">
         <is>
-          <t>PIF (Public Investment Fund)</t>
+          <t>Center3 (STC subsidiary); NEOM</t>
         </is>
       </c>
       <c r="N38" s="4" t="inlineStr">
         <is>
-          <t>Hyperscale datacenter; Cloud; AI infrastructure</t>
+          <t>OCI cloud (IaaS/PaaS); AI workloads; Sovereign AI; Enterprise</t>
         </is>
       </c>
       <c r="O38" s="4" t="inlineStr">
         <is>
-          <t>TBD (partnership since May 2023)</t>
+          <t>Jeddah live (2020); Riyadh live (2024); NEOM planned</t>
         </is>
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>Partnership with Saudi PIF for DC development in KSA and GCC</t>
+          <t>2 live cloud regions; OCI Supercluster (4,000+ Blackwell GPUs); 3rd region at NEOM planned</t>
         </is>
       </c>
       <c r="Q38" s="4" t="inlineStr">
         <is>
-          <t>DigitalBridge-PIF partnership May 2023; 12 GW global pipeline; DBP III fund $11.7B</t>
+          <t>Oracle $1.5B Saudi commitment; 5th ME region; first OCI Supercluster in ME Nov 2025</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>PE / Financial</t>
+          <t>Technology / Infrastructure</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>SoftBank</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -3059,68 +3045,62 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>Abu Dhabi (Stargate UAE partner)</t>
+          <t>Dubai / Abu Dhabi (+ Stargate UAE operator)</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="F39" s="4" t="n">
-        <v>0</v>
-      </c>
+          <t>Live + Expanding</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="n"/>
       <c r="G39" s="4" t="n">
         <v>200</v>
       </c>
-      <c r="H39" s="4" t="n">
-        <v>200</v>
-      </c>
-      <c r="I39" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="H39" s="4" t="n"/>
+      <c r="I39" s="4" t="n"/>
       <c r="J39" s="4" t="n">
         <v>0.2</v>
       </c>
-      <c r="K39" s="4" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="L39" s="4" t="n"/>
+      <c r="K39" s="4" t="n"/>
+      <c r="L39" s="4" t="n">
+        <v>1.5</v>
+      </c>
       <c r="M39" s="4" t="inlineStr">
         <is>
-          <t>G42 / OpenAI / Oracle / Nvidia / Cisco</t>
+          <t>G42 / OpenAI / SoftBank / Nvidia / Cisco</t>
         </is>
       </c>
       <c r="N39" s="4" t="inlineStr">
         <is>
-          <t>AI infrastructure; Stargate UAE co-investor/partner</t>
+          <t>OCI cloud; AI workloads; Stargate UAE operator alongside OpenAI</t>
         </is>
       </c>
       <c r="O39" s="4" t="inlineStr">
         <is>
-          <t>2026 (200 MW phase 1)</t>
+          <t>Live (2020); Stargate 200 MW Q3 2026</t>
         </is>
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>Stargate UAE consortium partner; 5 GW ultimate campus capacity</t>
+          <t>2 live UAE regions (Dubai, Abu Dhabi); fivefold capacity expansion; 4,000+ Blackwell GPUs; Stargate operator</t>
         </is>
       </c>
       <c r="Q39" s="4" t="inlineStr">
         <is>
-          <t>SoftBank is founding partner of Stargate UAE; announced May 2025</t>
+          <t>Oracle 2 UAE regions live; fivefold expansion; $1.5B+ 5-yr regional capex; Stargate UAE operator</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>PE / Financial</t>
+          <t>Technology / Infrastructure</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
@@ -3130,7 +3110,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>Abu Dhabi (Stargate UAE partner)</t>
+          <t>Abu Dhabi (Stargate UAE)</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -3141,123 +3121,806 @@
       <c r="F40" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G40" s="4" t="n">
-        <v>200</v>
-      </c>
-      <c r="H40" s="4" t="n">
-        <v>200</v>
-      </c>
+      <c r="G40" s="4" t="n"/>
+      <c r="H40" s="4" t="n"/>
       <c r="I40" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="J40" s="4" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="K40" s="4" t="n">
-        <v>0.2</v>
-      </c>
+      <c r="J40" s="4" t="n"/>
+      <c r="K40" s="4" t="n"/>
       <c r="L40" s="4" t="n"/>
       <c r="M40" s="4" t="inlineStr">
         <is>
-          <t>G42 / OpenAI / SoftBank / Nvidia / Cisco</t>
+          <t>G42 / OpenAI / Oracle / SoftBank / Nvidia</t>
         </is>
       </c>
       <c r="N40" s="4" t="inlineStr">
         <is>
-          <t>Cloud infrastructure (OCI); AI workloads; Stargate UAE operator</t>
+          <t>Networking; Security (zero-trust); Observability for OpenAI workloads</t>
         </is>
       </c>
       <c r="O40" s="4" t="inlineStr">
         <is>
-          <t>2026 (200 MW phase 1)</t>
+          <t>2026 (Stargate UAE ph1)</t>
         </is>
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>Stargate UAE operator alongside OpenAI; Oracle Cloud Infrastructure</t>
+          <t>Preferred technology partner; AI-ready networking &amp; security infrastructure</t>
         </is>
       </c>
       <c r="Q40" s="4" t="inlineStr">
         <is>
-          <t>Oracle is operator/partner in Stargate UAE; also operates Saudi cloud region</t>
+          <t>Cisco joined Stargate UAE May 2025; zero-trust security and AI-ready connectivity</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
+          <t>Technology / Infrastructure</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>Cisco</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>HUMAIN facilities (AMD/Cisco/HUMAIN JV)</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H41" s="4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K41" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L41" s="4" t="n"/>
+      <c r="M41" s="4" t="inlineStr">
+        <is>
+          <t>HUMAIN (PIF) / AMD (JV partner)</t>
+        </is>
+      </c>
+      <c r="N41" s="4" t="inlineStr">
+        <is>
+          <t>Networking; Infrastructure solutions for AMD GPU deployments</t>
+        </is>
+      </c>
+      <c r="O41" s="4" t="inlineStr">
+        <is>
+          <t>2026 (100 MW ph1); 1 GW by 2030</t>
+        </is>
+      </c>
+      <c r="P41" s="4" t="inlineStr">
+        <is>
+          <t>JV with AMD and HUMAIN; critical infra for Instinct MI450 clusters</t>
+        </is>
+      </c>
+      <c r="Q41" s="4" t="inlineStr">
+        <is>
+          <t>AMD/Cisco/HUMAIN JV Nov 2025; founding investor</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Technology / Infrastructure</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>SoftBank</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>Abu Dhabi (Stargate UAE)</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="H42" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="I42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" s="4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="K42" s="4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L42" s="4" t="n"/>
+      <c r="M42" s="4" t="inlineStr">
+        <is>
+          <t>G42 / OpenAI / Oracle / Nvidia / Cisco</t>
+        </is>
+      </c>
+      <c r="N42" s="4" t="inlineStr">
+        <is>
+          <t>AI infrastructure co-investor; Stargate UAE founding partner</t>
+        </is>
+      </c>
+      <c r="O42" s="4" t="inlineStr">
+        <is>
+          <t>Q3 2026 (200 MW ph1)</t>
+        </is>
+      </c>
+      <c r="P42" s="4" t="inlineStr">
+        <is>
+          <t>Stargate UAE consortium partner; broader $500B Stargate program</t>
+        </is>
+      </c>
+      <c r="Q42" s="4" t="inlineStr">
+        <is>
+          <t>SoftBank founding partner Stargate UAE May 2025; $500B global Stargate by 2029</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="16" t="inlineStr">
+        <is>
+          <t>PRIVATE EQUITY &amp; FINANCIAL SPONSORS</t>
+        </is>
+      </c>
+      <c r="B43" s="17" t="inlineStr"/>
+      <c r="C43" s="17" t="inlineStr"/>
+      <c r="D43" s="17" t="inlineStr"/>
+      <c r="E43" s="17" t="inlineStr"/>
+      <c r="F43" s="17" t="inlineStr"/>
+      <c r="G43" s="17" t="inlineStr"/>
+      <c r="H43" s="17" t="inlineStr"/>
+      <c r="I43" s="17" t="inlineStr"/>
+      <c r="J43" s="17" t="inlineStr"/>
+      <c r="K43" s="17" t="inlineStr"/>
+      <c r="L43" s="17" t="inlineStr"/>
+      <c r="M43" s="17" t="inlineStr"/>
+      <c r="N43" s="17" t="inlineStr"/>
+      <c r="O43" s="17" t="inlineStr"/>
+      <c r="P43" s="17" t="inlineStr"/>
+      <c r="Q43" s="17" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
           <t>PE / Financial</t>
         </is>
       </c>
-      <c r="B41" s="4" t="inlineStr">
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>KKR</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>Dubai (+ GCC expansion)</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>Live + Expanding</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="n">
+        <v>150</v>
+      </c>
+      <c r="G44" s="4" t="n">
+        <v>350</v>
+      </c>
+      <c r="H44" s="4" t="n">
+        <v>500</v>
+      </c>
+      <c r="I44" s="4" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="J44" s="4" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="K44" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L44" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="M44" s="4" t="inlineStr">
+        <is>
+          <t>Gulf Data Hub</t>
+        </is>
+      </c>
+      <c r="N44" s="4" t="inlineStr">
+        <is>
+          <t>Colocation; Hyperscale; Cloud; AI-ready</t>
+        </is>
+      </c>
+      <c r="O44" s="4" t="inlineStr">
+        <is>
+          <t>7 DCs live; GCC-wide expansion</t>
+        </is>
+      </c>
+      <c r="P44" s="4" t="inlineStr">
+        <is>
+          <t>Gulf Data Hub: 7 DCs in UAE &amp; Saudi; expanding to Kuwait, Qatar, Bahrain, Oman</t>
+        </is>
+      </c>
+      <c r="Q44" s="4" t="inlineStr">
+        <is>
+          <t>KKR stake in GDH Jan 2025; $5B+ commitment; first ME DC investment</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>PE / Financial</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>KKR</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>Various (Gulf Data Hub)</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>Live + Expanding</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="n"/>
+      <c r="G45" s="4" t="n"/>
+      <c r="H45" s="4" t="n"/>
+      <c r="I45" s="4" t="n"/>
+      <c r="J45" s="4" t="n"/>
+      <c r="K45" s="4" t="n"/>
+      <c r="L45" s="4" t="n"/>
+      <c r="M45" s="4" t="inlineStr">
+        <is>
+          <t>Gulf Data Hub</t>
+        </is>
+      </c>
+      <c r="N45" s="4" t="inlineStr">
+        <is>
+          <t>Colocation; Hyperscale; Enterprise</t>
+        </is>
+      </c>
+      <c r="O45" s="4" t="inlineStr">
+        <is>
+          <t>Existing + expansion</t>
+        </is>
+      </c>
+      <c r="P45" s="4" t="inlineStr">
+        <is>
+          <t>Part of GDH GCC platform</t>
+        </is>
+      </c>
+      <c r="Q45" s="4" t="inlineStr">
+        <is>
+          <t>GDH existing Saudi operations; expansion under KKR</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>PE / Financial</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>Blackstone (via AirTrunk)</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>TBD (HUMAIN campus)</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" s="4" t="n"/>
+      <c r="H46" s="4" t="n"/>
+      <c r="I46" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" s="4" t="n"/>
+      <c r="K46" s="4" t="n"/>
+      <c r="L46" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="M46" s="4" t="inlineStr">
+        <is>
+          <t>HUMAIN (PIF) / AirTrunk</t>
+        </is>
+      </c>
+      <c r="N46" s="4" t="inlineStr">
+        <is>
+          <t>Hyperscale AI-ready DC</t>
+        </is>
+      </c>
+      <c r="O46" s="4" t="inlineStr">
+        <is>
+          <t>2026 (initial phase)</t>
+        </is>
+      </c>
+      <c r="P46" s="4" t="inlineStr">
+        <is>
+          <t>Large-scale campus; AirTrunk's 1st ME project</t>
+        </is>
+      </c>
+      <c r="Q46" s="4" t="inlineStr">
+        <is>
+          <t>HUMAIN-AirTrunk $3B Oct 2025; Blackstone + CPPIB back AirTrunk</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>PE / Financial</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>BlackRock (GIP / AIP)</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>Abu Dhabi (via MGX/AIP partnership)</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>Planned (indirect)</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" s="4" t="n"/>
+      <c r="H47" s="4" t="n"/>
+      <c r="I47" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" s="4" t="n"/>
+      <c r="K47" s="4" t="n"/>
+      <c r="L47" s="4" t="inlineStr">
+        <is>
+          <t>30-100 (AIP total)</t>
+        </is>
+      </c>
+      <c r="M47" s="4" t="inlineStr">
+        <is>
+          <t>MGX / Microsoft / Nvidia (AIP partners)</t>
+        </is>
+      </c>
+      <c r="N47" s="4" t="inlineStr">
+        <is>
+          <t>AI infrastructure investment via AIP; DC acquisition and development</t>
+        </is>
+      </c>
+      <c r="O47" s="4" t="inlineStr">
+        <is>
+          <t>Ongoing (AIP since Sep 2024)</t>
+        </is>
+      </c>
+      <c r="P47" s="4" t="inlineStr">
+        <is>
+          <t>AIP: $30B equity, up to $100B w/ debt; Aligned DC $40B acq; Kuwait IA + Temasek as LPs</t>
+        </is>
+      </c>
+      <c r="Q47" s="4" t="inlineStr">
+        <is>
+          <t>BlackRock GIP co-founded AIP Sep 2024 w/ MGX, MSFT, NVDA; Aligned 5 GW portfolio; Gulf-linked via MGX</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>PE / Financial</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>Silver Lake</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>Abu Dhabi / Dubai (via Khazna + G42)</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>Live + Expanding</t>
+        </is>
+      </c>
+      <c r="F48" s="4" t="n">
+        <v>263</v>
+      </c>
+      <c r="G48" s="4" t="n">
+        <v>175</v>
+      </c>
+      <c r="H48" s="4" t="n">
+        <v>438</v>
+      </c>
+      <c r="I48" s="4" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="J48" s="4" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="K48" s="4" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="L48" s="4" t="n"/>
+      <c r="M48" s="4" t="inlineStr">
+        <is>
+          <t>Khazna Data Centers / G42</t>
+        </is>
+      </c>
+      <c r="N48" s="4" t="inlineStr">
+        <is>
+          <t>Wholesale colocation; Hyperscale; AI-ready</t>
+        </is>
+      </c>
+      <c r="O48" s="4" t="inlineStr">
+        <is>
+          <t>263 MW live; 175 MW building</t>
+        </is>
+      </c>
+      <c r="P48" s="4" t="inlineStr">
+        <is>
+          <t>Minority stake in Khazna (alongside MGX, G42); also investor in G42</t>
+        </is>
+      </c>
+      <c r="Q48" s="4" t="inlineStr">
+        <is>
+          <t>Silver Lake acquired Khazna stake Mar 2025; also backs G42</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>PE / Financial</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>Brookfield</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>Qatar</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" s="4" t="n"/>
+      <c r="H49" s="4" t="n"/>
+      <c r="I49" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" s="4" t="n"/>
+      <c r="K49" s="4" t="n"/>
+      <c r="L49" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="M49" s="4" t="inlineStr">
+        <is>
+          <t>Qai (Qatar AI) / QIA</t>
+        </is>
+      </c>
+      <c r="N49" s="4" t="inlineStr">
+        <is>
+          <t>AI infrastructure; High-performance compute; Data handling</t>
+        </is>
+      </c>
+      <c r="O49" s="4" t="inlineStr">
+        <is>
+          <t>TBD (JV Dec 2025)</t>
+        </is>
+      </c>
+      <c r="P49" s="4" t="inlineStr">
+        <is>
+          <t>$20B JV w/ Qai; backed by Gov of Qatar + QIA</t>
+        </is>
+      </c>
+      <c r="Q49" s="4" t="inlineStr">
+        <is>
+          <t>Brookfield-Qai $20B AI JV Dec 2025; Nvidia backer (Rubin chips); part of $100B AI fund</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>PE / Financial</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>Brookfield</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>Various</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" s="4" t="n"/>
+      <c r="H50" s="4" t="n"/>
+      <c r="I50" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" s="4" t="n"/>
+      <c r="K50" s="4" t="n"/>
+      <c r="L50" s="4" t="n"/>
+      <c r="M50" s="4" t="inlineStr">
+        <is>
+          <t>Ori Industries (acquired)</t>
+        </is>
+      </c>
+      <c r="N50" s="4" t="inlineStr">
+        <is>
+          <t>AI cloud; Edge computing; Distributed AI</t>
+        </is>
+      </c>
+      <c r="O50" s="4" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="P50" s="4" t="inlineStr">
+        <is>
+          <t>Acquired Ori Industries; merged into Radiant Infra</t>
+        </is>
+      </c>
+      <c r="Q50" s="4" t="inlineStr">
+        <is>
+          <t>Saudi Aramco Wa'ed-backed startup; Brookfield $100B AI infra program</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>PE / Financial</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>DigitalBridge</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" s="4" t="n"/>
+      <c r="H51" s="4" t="n"/>
+      <c r="I51" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" s="4" t="n"/>
+      <c r="K51" s="4" t="n"/>
+      <c r="L51" s="4" t="n"/>
+      <c r="M51" s="4" t="inlineStr">
+        <is>
+          <t>PIF (Public Investment Fund)</t>
+        </is>
+      </c>
+      <c r="N51" s="4" t="inlineStr">
+        <is>
+          <t>Hyperscale DC; Cloud; AI</t>
+        </is>
+      </c>
+      <c r="O51" s="4" t="inlineStr">
+        <is>
+          <t>TBD (partnership since May 2023)</t>
+        </is>
+      </c>
+      <c r="P51" s="4" t="inlineStr">
+        <is>
+          <t>PIF partnership; 12 GW global pipeline; DBP III fund $11.7B</t>
+        </is>
+      </c>
+      <c r="Q51" s="4" t="inlineStr">
+        <is>
+          <t>DigitalBridge-PIF May 2023; $11.7B fund; DC + towers + fiber</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>PE / Financial</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
         <is>
           <t>DataVolt (Vision Invest)</t>
         </is>
       </c>
-      <c r="C41" s="4" t="inlineStr">
+      <c r="C52" s="4" t="inlineStr">
         <is>
           <t>Saudi Arabia</t>
         </is>
       </c>
-      <c r="D41" s="4" t="inlineStr">
+      <c r="D52" s="4" t="inlineStr">
         <is>
           <t>NEOM / Oxagon</t>
         </is>
       </c>
-      <c r="E41" s="5" t="inlineStr">
+      <c r="E52" s="5" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
       </c>
-      <c r="F41" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G41" s="4" t="n">
+      <c r="F52" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" s="4" t="n">
         <v>300</v>
       </c>
-      <c r="H41" s="4" t="n">
+      <c r="H52" s="4" t="n">
         <v>300</v>
       </c>
-      <c r="I41" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" s="4" t="n">
+      <c r="I52" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" s="4" t="n">
         <v>0.3</v>
       </c>
-      <c r="K41" s="4" t="n">
+      <c r="K52" s="4" t="n">
         <v>0.3</v>
       </c>
-      <c r="L41" s="4" t="n">
+      <c r="L52" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="M41" s="4" t="inlineStr">
+      <c r="M52" s="4" t="inlineStr">
         <is>
           <t>NEOM</t>
         </is>
       </c>
-      <c r="N41" s="4" t="inlineStr">
-        <is>
-          <t>Net-zero AI datacenter; Renewable-powered compute; AI training</t>
-        </is>
-      </c>
-      <c r="O41" s="4" t="inlineStr">
-        <is>
-          <t>2028 (first 300 MW phase); 1.5 GW ultimate</t>
-        </is>
-      </c>
-      <c r="P41" s="4" t="inlineStr">
-        <is>
-          <t>1.5 GW net-zero AI campus at Oxagon; LG Electronics cooling systems; sub-sea cable connectivity</t>
-        </is>
-      </c>
-      <c r="Q41" s="4" t="inlineStr">
-        <is>
-          <t>DataVolt-NEOM $5B agreement Feb 2025; first 300 MW by 2028; wholly owned by Vision Invest</t>
+      <c r="N52" s="4" t="inlineStr">
+        <is>
+          <t>Net-zero AI DC; Renewable compute; AI training</t>
+        </is>
+      </c>
+      <c r="O52" s="4" t="inlineStr">
+        <is>
+          <t>2028 (300 MW ph1); 1.5 GW ultimate</t>
+        </is>
+      </c>
+      <c r="P52" s="4" t="inlineStr">
+        <is>
+          <t>1.5 GW net-zero at Oxagon; LG cooling; sub-sea cables; renewable energy</t>
+        </is>
+      </c>
+      <c r="Q52" s="4" t="inlineStr">
+        <is>
+          <t>DataVolt-NEOM $5B Feb 2025; Vision Invest (Acwa Power parent)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q41"/>
+  <autoFilter ref="A1:Q52"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3268,21 +3931,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L22"/>
+  <dimension ref="A1:L32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="58" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="50" customWidth="1" min="11" max="11"/>
-    <col width="75" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="52" customWidth="1" min="11" max="11"/>
+    <col width="80" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3303,27 +3966,27 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Total Live Capacity (MW)</t>
+          <t>Live (MW)</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Total Planned Capacity (MW)</t>
+          <t>Planned (MW)</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Total Capacity (MW)</t>
+          <t>Total (MW)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Total Live (GW)</t>
+          <t>Live (GW)</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Total Planned (GW)</t>
+          <t>Planned (GW)</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -3333,12 +3996,12 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Total Investment ($B)</t>
+          <t>Investment ($B)</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Primary Workload Focus</t>
+          <t>Primary Workloads</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
@@ -3378,7 +4041,7 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>UAE (Live), Saudi Arabia (Planned Q4 2026), Qatar (Live), Kuwait (Planned)</t>
+          <t>UAE (Live), Saudi (Planned Q4 2026), Qatar (Live), Kuwait (Planned)</t>
         </is>
       </c>
       <c r="D3" s="4" t="n">
@@ -3406,12 +4069,12 @@
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>Azure cloud IaaS/PaaS/SaaS; AI/ML; Enterprise; Government sovereign cloud</t>
+          <t>Azure IaaS/PaaS/SaaS; AI/ML; Enterprise; Sovereign cloud</t>
         </is>
       </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
-          <t>Deepest Gulf presence among Mag7. Live in 3 countries, planned in 4. Largest single investment ($15.2B UAE). Strong government partnerships.</t>
+          <t>Deepest Mag7 Gulf presence. Live in 3 countries, 4 planned. Largest investment ($15.2B UAE).</t>
         </is>
       </c>
     </row>
@@ -3428,7 +4091,7 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>UAE (Live), Bahrain (Live), Saudi Arabia (Planned 2026), Oman (Edge), Qatar (Edge)</t>
+          <t>UAE (Live), Bahrain (Live), Saudi (Planned 2026), Oman/Qatar (Edge)</t>
         </is>
       </c>
       <c r="D4" s="4" t="n">
@@ -3456,12 +4119,12 @@
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>AWS full cloud stack; AI/ML (SageMaker); Enterprise; Edge computing</t>
+          <t>AWS full stack; AI/ML; Enterprise; Edge</t>
         </is>
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
-          <t>Broadest geographic coverage (5 Gulf states). First mover in ME (Bahrain 2019). $5.3B Saudi expansion in pipeline.</t>
+          <t>Broadest geographic reach (5 states). First mover (Bahrain 2019). HUMAIN preferred AI partner.</t>
         </is>
       </c>
     </row>
@@ -3478,7 +4141,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Saudi Arabia (Live), Qatar (Live), UAE (Under Discussion), Kuwait (Planned)</t>
+          <t>Saudi (Live), Qatar (Live), UAE (Discussion), Kuwait (Planned)</t>
         </is>
       </c>
       <c r="D5" s="4" t="n">
@@ -3498,12 +4161,12 @@
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>Google Cloud full stack; AI/ML; Data analytics; Enterprise</t>
+          <t>Google Cloud; AI/ML; Analytics; Enterprise</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t>Two live GCC regions. Evaluating UAE and Kuwait. Reportedly in advanced Stargate UAE tenant talks.</t>
+          <t>2 live GCC regions. Advanced Stargate tenant talks. Smaller disclosed investment.</t>
         </is>
       </c>
     </row>
@@ -3520,7 +4183,7 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Saudi Arabia (Planned, partially live Q1 2026), UAE (Planned 2026)</t>
+          <t>Saudi (Planned/live Q1 2026), UAE (Planned 2026)</t>
         </is>
       </c>
       <c r="D6" s="4" t="n">
@@ -3543,17 +4206,17 @@
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>~18-24 (GPU supply)</t>
+          <t>~18-24 (GPU)</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>AI model training; AI inference; GPU-accelerated computing; Sovereign AI factories</t>
+          <t>AI training/inference; GPU computing; Sovereign AI</t>
         </is>
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
-          <t>Largest planned capacity (~700 MW). Strategic GPU supply partnerships with HUMAIN (Saudi) and Stargate UAE.</t>
+          <t>Largest Mag7 planned capacity (~700 MW). GPU supplier to HUMAIN + Stargate UAE.</t>
         </is>
       </c>
     </row>
@@ -3570,7 +4233,7 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>UAE (Under Discussion — Stargate UAE tenancy)</t>
+          <t>UAE (Discussion)</t>
         </is>
       </c>
       <c r="D7" s="4" t="n">
@@ -3585,17 +4248,17 @@
       <c r="I7" s="4" t="n"/>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>None confirmed</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>Potential: AI training/inference (Llama models)</t>
+          <t>Potential: AI training/inference (Llama)</t>
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
-          <t>Minimal Gulf exposure. Only preliminary tenant discussions at Stargate UAE.</t>
+          <t>Minimal. Preliminary Stargate tenant talks only.</t>
         </is>
       </c>
     </row>
@@ -3645,7 +4308,7 @@
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t>No datacenter presence in any Gulf state.</t>
+          <t>Zero Gulf DC presence.</t>
         </is>
       </c>
     </row>
@@ -3662,7 +4325,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>None (xAI is separate entity)</t>
+          <t>None (xAI separate)</t>
         </is>
       </c>
       <c r="D9" s="4" t="n">
@@ -3695,14 +4358,14 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>No direct datacenter presence. xAI (separate co.) has 500 MW Saudi deal.</t>
+          <t>No direct DC. xAI (separate co.) has 500 MW Saudi deal.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>AI LABS</t>
+          <t>AI LABS (OpenAI, Anthropic, xAI)</t>
         </is>
       </c>
       <c r="B10" s="10" t="inlineStr"/>
@@ -3753,17 +4416,17 @@
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>N/A (consortium-funded)</t>
+          <t>N/A (consortium)</t>
         </is>
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>AI model training &amp; inference (GPT); OpenAI for Countries</t>
+          <t>AI training/inference (GPT); OpenAI for Countries</t>
         </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
-          <t>Major Gulf commitment via Stargate UAE (1 GW, expanding to 5 GW). First international Stargate. 200 MW phase 1 in Q3 2026.</t>
+          <t>Major via Stargate UAE (1 GW → 5 GW). First intl Stargate. &gt;$30B total cost.</t>
         </is>
       </c>
     </row>
@@ -3780,7 +4443,7 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>UAE &amp; Bahrain (indirect, via AWS Bedrock cross-region inference)</t>
+          <t>UAE &amp; Bahrain (indirect via AWS Bedrock)</t>
         </is>
       </c>
       <c r="D12" s="4" t="n">
@@ -3808,12 +4471,12 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>Claude model inference via Amazon Bedrock (indirect)</t>
+          <t>Claude inference via Bedrock (indirect)</t>
         </is>
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
-          <t>No owned Gulf infrastructure. Models available via AWS UAE/Bahrain. $50B DC plan focuses on US only.</t>
+          <t>No owned Gulf infra. $50B plan is US-only.</t>
         </is>
       </c>
     </row>
@@ -3830,7 +4493,7 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Saudi Arabia (Planned 2026-27), UAE (Under Discussion)</t>
+          <t>Saudi (Planned), UAE (Discussion)</t>
         </is>
       </c>
       <c r="D13" s="4" t="n">
@@ -3858,411 +4521,811 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>AI model training (Grok); AI inference; GPU computing</t>
+          <t>AI training (Grok); GPU computing</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
-          <t>500 MW Saudi deal with HUMAIN. Potential Stargate UAE tenant. Not publicly traded.</t>
+          <t>500 MW Saudi HUMAIN deal. Potential Stargate tenant.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="inlineStr">
-        <is>
-          <t>PRIVATE EQUITY &amp; FINANCIAL SPONSORS</t>
-        </is>
-      </c>
-      <c r="B14" s="12" t="inlineStr"/>
-      <c r="C14" s="12" t="inlineStr"/>
-      <c r="D14" s="12" t="inlineStr"/>
-      <c r="E14" s="12" t="inlineStr"/>
-      <c r="F14" s="12" t="inlineStr"/>
-      <c r="G14" s="12" t="inlineStr"/>
-      <c r="H14" s="12" t="inlineStr"/>
-      <c r="I14" s="12" t="inlineStr"/>
-      <c r="J14" s="12" t="inlineStr"/>
-      <c r="K14" s="12" t="inlineStr"/>
-      <c r="L14" s="12" t="inlineStr"/>
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>SOVEREIGN WEALTH FUNDS &amp; STATE ENTITIES (Mubadala, G42, HUMAIN, MGX)</t>
+        </is>
+      </c>
+      <c r="B14" s="13" t="inlineStr"/>
+      <c r="C14" s="13" t="inlineStr"/>
+      <c r="D14" s="13" t="inlineStr"/>
+      <c r="E14" s="13" t="inlineStr"/>
+      <c r="F14" s="13" t="inlineStr"/>
+      <c r="G14" s="13" t="inlineStr"/>
+      <c r="H14" s="13" t="inlineStr"/>
+      <c r="I14" s="13" t="inlineStr"/>
+      <c r="J14" s="13" t="inlineStr"/>
+      <c r="K14" s="13" t="inlineStr"/>
+      <c r="L14" s="13" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>PE / Financial</t>
+          <t>Sovereign Wealth / State</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>KKR</t>
+          <t>Mubadala</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>UAE (Live), Saudi Arabia (Live + Expanding), GCC-wide expansion planned</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="n">
-        <v>150</v>
-      </c>
-      <c r="E15" s="4" t="n">
-        <v>350</v>
-      </c>
-      <c r="F15" s="4" t="n">
-        <v>500</v>
-      </c>
-      <c r="G15" s="4" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="H15" s="4" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="I15" s="4" t="n">
-        <v>0.5</v>
-      </c>
+          <t>UAE (via G42, MGX — indirect)</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="n"/>
+      <c r="E15" s="4" t="n"/>
+      <c r="F15" s="4" t="n"/>
+      <c r="G15" s="4" t="n"/>
+      <c r="H15" s="4" t="n"/>
+      <c r="I15" s="4" t="n"/>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>5.0+</t>
+          <t>N/A (principal backer)</t>
         </is>
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>Colocation; Hyperscale; Cloud; AI-ready infrastructure</t>
+          <t>Sovereign backing for G42/Khazna/MGX ecosystem; semiconductors (GlobalFoundries)</t>
         </is>
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
-          <t>Via Gulf Data Hub platform. 7 live DCs. $5B+ commitment. Expanding to all 6 GCC states.</t>
+          <t>Indirect via G42 (backer), MGX (co-founder). GlobalFoundries 81% stake ($16B expansion). $1.4T US infra pledge.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>PE / Financial</t>
+          <t>Sovereign Wealth / State</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Blackstone (via AirTrunk)</t>
+          <t>G42</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Saudi Arabia (Planned 2026)</t>
+          <t>UAE (Live + Expanding), Saudi (Planned)</t>
         </is>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" s="4" t="n"/>
-      <c r="F16" s="4" t="n"/>
+        <v>263</v>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>937</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>1200</v>
+      </c>
       <c r="G16" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" s="4" t="n"/>
-      <c r="I16" s="4" t="n"/>
+        <v>0.26</v>
+      </c>
+      <c r="H16" s="4" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="I16" s="4" t="n">
+        <v>1.2</v>
+      </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>Hyperscale AI-ready datacenter</t>
+          <t>Hyperscale (Khazna); AI cloud (Core42); Stargate developer; MSFT Azure partner</t>
         </is>
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
-          <t>AirTrunk-HUMAIN $3B partnership. First Middle East entry. Part of HUMAIN's 1.9 GW-by-2030 plan.</t>
+          <t>Central node of UAE DC ecosystem. Stargate UAE developer. Khazna ~$5.5B. 30 DCs, 263 MW live, 1 GW+ building.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>PE / Financial</t>
+          <t>Sovereign Wealth / State</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Silver Lake + MGX</t>
+          <t>HUMAIN (PIF)</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>UAE (Live), Saudi Arabia (Planned)</t>
+          <t>Saudi Arabia (Planned, partially live early 2026)</t>
         </is>
       </c>
       <c r="D17" s="4" t="n">
-        <v>263</v>
+        <v>100</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>175</v>
+        <v>1800</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>438</v>
+        <v>1900</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.26</v>
+        <v>0.1</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.18</v>
+        <v>1.8</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.44</v>
+        <v>1.9</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>~5.5 (valuation)</t>
+          <t>~77 (total est.)</t>
         </is>
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>Wholesale colocation; Hyperscale; AI-ready</t>
+          <t>National AI platform; sovereign AI; GPU computing; multi-vendor</t>
         </is>
       </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
-          <t>Via Khazna Data Centers. 263 MW live, 175 MW building. Targeting 2+ GW in Saudi Arabia.</t>
+          <t>Largest Gulf DC buildout. 1.9 GW by 2030, 6.6 GW by 2034. Partners: Nvidia, AMD, Cisco, xAI, AirTrunk, AWS, STC. $10B VC fund.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>PE / Financial</t>
+          <t>Sovereign Wealth / State</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Brookfield</t>
+          <t>MGX</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Qatar (Planned — $20B JV), Saudi Arabia (Planned)</t>
+          <t>UAE (Live via Khazna); Global (AIP)</t>
         </is>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0</v>
+        <v>263</v>
       </c>
       <c r="E18" s="4" t="n"/>
       <c r="F18" s="4" t="n"/>
       <c r="G18" s="4" t="n">
-        <v>0</v>
+        <v>0.26</v>
       </c>
       <c r="H18" s="4" t="n"/>
       <c r="I18" s="4" t="n"/>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>20.0+</t>
+          <t>~5.5 (Khazna val.)</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>AI infrastructure; High-performance compute</t>
+          <t>AI infra investing; DC portfolio; AIP anchor</t>
         </is>
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
-          <t>Largest single PE commitment ($20B Qatar JV with Qai). Saudi entry via Ori Industries acquisition. Part of $100B AI fund.</t>
+          <t>$100B AI fund. Khazna minority stake. AIP w/ BlackRock ($30-100B). Aligned $40B acq. Paris 1.4 GW. Vantage 2.3 GW.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>PE / Financial</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>DigitalBridge</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>Saudi Arabia (Planned), GCC (Planned)</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" s="4" t="n"/>
-      <c r="F19" s="4" t="n"/>
-      <c r="G19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="4" t="n"/>
-      <c r="I19" s="4" t="n"/>
-      <c r="J19" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K19" s="4" t="inlineStr">
-        <is>
-          <t>Hyperscale datacenter; Cloud; AI</t>
-        </is>
-      </c>
-      <c r="L19" s="4" t="inlineStr">
-        <is>
-          <t>PIF partnership since 2023. 12 GW global pipeline. $11.7B fund (DBP III).</t>
-        </is>
-      </c>
+      <c r="A19" s="14" t="inlineStr">
+        <is>
+          <t>TECHNOLOGY &amp; INFRASTRUCTURE PARTNERS (Nvidia, AMD, Oracle, Cisco, SoftBank)</t>
+        </is>
+      </c>
+      <c r="B19" s="15" t="inlineStr"/>
+      <c r="C19" s="15" t="inlineStr"/>
+      <c r="D19" s="15" t="inlineStr"/>
+      <c r="E19" s="15" t="inlineStr"/>
+      <c r="F19" s="15" t="inlineStr"/>
+      <c r="G19" s="15" t="inlineStr"/>
+      <c r="H19" s="15" t="inlineStr"/>
+      <c r="I19" s="15" t="inlineStr"/>
+      <c r="J19" s="15" t="inlineStr"/>
+      <c r="K19" s="15" t="inlineStr"/>
+      <c r="L19" s="15" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>PE / Financial</t>
+          <t>Technology / Infrastructure</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>SoftBank</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>UAE (Planned — Stargate UAE partner)</t>
+          <t>Saudi (Planned/live), UAE (Planned)</t>
         </is>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>200</v>
+        <v>600</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>200</v>
+        <v>700</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>~18-24 (GPU)</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>AI infrastructure; Stargate UAE co-investor</t>
+          <t>GPU supply; AI training/inference; Sovereign AI</t>
         </is>
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
-          <t>Founding partner of Stargate UAE consortium.</t>
+          <t>GPU supplier to HUMAIN (500 MW, 600K chips) + Stargate UAE (100K chips ph1). Khazna Blackwell certified.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>PE / Financial</t>
+          <t>Technology / Infrastructure</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>UAE (Planned — Stargate UAE operator)</t>
+          <t>Saudi Arabia (Planned)</t>
         </is>
       </c>
       <c r="D21" s="4" t="n">
         <v>0</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="G21" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>OCI cloud; AI workloads; Stargate UAE operator</t>
+          <t>GPU (Instinct MI450); CPU (EPYC); DPU (Pensando); Edge (Ryzen AI)</t>
         </is>
       </c>
       <c r="L21" s="4" t="inlineStr">
         <is>
-          <t>Operator/partner in Stargate UAE. Also has existing Saudi cloud region.</t>
+          <t>$10B HUMAIN deal. AMD/Cisco/HUMAIN JV for 1 GW by 2030. Center of Excellence. Luma AI 1st customer.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
+          <t>Technology / Infrastructure</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>Oracle</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>Saudi (Live), UAE (Live + Expanding)</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="n"/>
+      <c r="E22" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="F22" s="4" t="n"/>
+      <c r="G22" s="4" t="n"/>
+      <c r="H22" s="4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I22" s="4" t="n"/>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>~3.0</t>
+        </is>
+      </c>
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>OCI cloud; AI (Blackwell Supercluster); Stargate UAE operator</t>
+        </is>
+      </c>
+      <c r="L22" s="4" t="inlineStr">
+        <is>
+          <t>3 live ME regions (Jeddah, Riyadh, Dubai/Abu Dhabi). Fivefold UAE expansion. Stargate operator. NEOM 3rd Saudi region.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Technology / Infrastructure</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Cisco</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>UAE (Planned), Saudi (Planned)</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F23" s="4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K23" s="4" t="inlineStr">
+        <is>
+          <t>Networking; Zero-trust security; Observability</t>
+        </is>
+      </c>
+      <c r="L23" s="4" t="inlineStr">
+        <is>
+          <t>Stargate UAE preferred tech partner. AMD/Cisco/HUMAIN JV (1 GW Saudi by 2030). Founding JV investor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Technology / Infrastructure</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>SoftBank</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>UAE (Planned — Stargate partner)</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="G24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I24" s="4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K24" s="4" t="inlineStr">
+        <is>
+          <t>AI infra co-investor; Stargate partner</t>
+        </is>
+      </c>
+      <c r="L24" s="4" t="inlineStr">
+        <is>
+          <t>Stargate UAE founding partner. Broader $500B Stargate program globally.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="16" t="inlineStr">
+        <is>
+          <t>PRIVATE EQUITY &amp; FINANCIAL SPONSORS</t>
+        </is>
+      </c>
+      <c r="B25" s="17" t="inlineStr"/>
+      <c r="C25" s="17" t="inlineStr"/>
+      <c r="D25" s="17" t="inlineStr"/>
+      <c r="E25" s="17" t="inlineStr"/>
+      <c r="F25" s="17" t="inlineStr"/>
+      <c r="G25" s="17" t="inlineStr"/>
+      <c r="H25" s="17" t="inlineStr"/>
+      <c r="I25" s="17" t="inlineStr"/>
+      <c r="J25" s="17" t="inlineStr"/>
+      <c r="K25" s="17" t="inlineStr"/>
+      <c r="L25" s="17" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
           <t>PE / Financial</t>
         </is>
       </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>KKR</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>UAE (Live), Saudi (Live + Expanding), GCC-wide</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="n">
+        <v>150</v>
+      </c>
+      <c r="E26" s="4" t="n">
+        <v>350</v>
+      </c>
+      <c r="F26" s="4" t="n">
+        <v>500</v>
+      </c>
+      <c r="G26" s="4" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H26" s="4" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="I26" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>5.0+</t>
+        </is>
+      </c>
+      <c r="K26" s="4" t="inlineStr">
+        <is>
+          <t>Colocation; Hyperscale; AI-ready</t>
+        </is>
+      </c>
+      <c r="L26" s="4" t="inlineStr">
+        <is>
+          <t>Via Gulf Data Hub. 7 live DCs. $5B+ commitment. Expanding to all 6 GCC states.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>PE / Financial</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>Blackstone (AirTrunk)</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>Saudi (Planned 2026)</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="4" t="n"/>
+      <c r="F27" s="4" t="n"/>
+      <c r="G27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="4" t="n"/>
+      <c r="I27" s="4" t="n"/>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="K27" s="4" t="inlineStr">
+        <is>
+          <t>Hyperscale AI-ready DC</t>
+        </is>
+      </c>
+      <c r="L27" s="4" t="inlineStr">
+        <is>
+          <t>AirTrunk-HUMAIN $3B. AirTrunk's 1st ME entry.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>PE / Financial</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>BlackRock (GIP/AIP)</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>UAE (indirect via MGX/AIP)</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="4" t="n"/>
+      <c r="F28" s="4" t="n"/>
+      <c r="G28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="4" t="n"/>
+      <c r="I28" s="4" t="n"/>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>30-100 (AIP)</t>
+        </is>
+      </c>
+      <c r="K28" s="4" t="inlineStr">
+        <is>
+          <t>AI infra investment via AIP</t>
+        </is>
+      </c>
+      <c r="L28" s="4" t="inlineStr">
+        <is>
+          <t>AIP w/ MGX, MSFT, NVDA. Aligned $40B. Kuwait IA + Temasek as LPs. Gulf-linked via MGX.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>PE / Financial</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>Silver Lake</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>UAE (Live via Khazna + G42)</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="n">
+        <v>263</v>
+      </c>
+      <c r="E29" s="4" t="n">
+        <v>175</v>
+      </c>
+      <c r="F29" s="4" t="n">
+        <v>438</v>
+      </c>
+      <c r="G29" s="4" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="H29" s="4" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="I29" s="4" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K29" s="4" t="inlineStr">
+        <is>
+          <t>Wholesale colo; Hyperscale; AI-ready</t>
+        </is>
+      </c>
+      <c r="L29" s="4" t="inlineStr">
+        <is>
+          <t>Khazna minority stake. Also G42 investor. Enabling Stargate UAE build.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>PE / Financial</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>Brookfield</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>Qatar (Planned $20B JV), Saudi (Planned)</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="4" t="n"/>
+      <c r="F30" s="4" t="n"/>
+      <c r="G30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="4" t="n"/>
+      <c r="I30" s="4" t="n"/>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>20.0+</t>
+        </is>
+      </c>
+      <c r="K30" s="4" t="inlineStr">
+        <is>
+          <t>AI infra; HPC; Edge computing</t>
+        </is>
+      </c>
+      <c r="L30" s="4" t="inlineStr">
+        <is>
+          <t>Largest PE commitment ($20B Qatar JV). Saudi via Ori/Radiant. Nvidia-backed (Rubin chips).</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>PE / Financial</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>DigitalBridge</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>Saudi/GCC (Planned)</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="4" t="n"/>
+      <c r="F31" s="4" t="n"/>
+      <c r="G31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="4" t="n"/>
+      <c r="I31" s="4" t="n"/>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K31" s="4" t="inlineStr">
+        <is>
+          <t>Hyperscale DC; Cloud; AI</t>
+        </is>
+      </c>
+      <c r="L31" s="4" t="inlineStr">
+        <is>
+          <t>PIF partnership since 2023. 12 GW global pipeline. $11.7B fund.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>PE / Financial</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
         <is>
           <t>DataVolt (Vision Invest)</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>Saudi Arabia (Planned 2028)</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" s="4" t="n">
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>Saudi (Planned 2028)</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="4" t="n">
         <v>300</v>
       </c>
-      <c r="F22" s="4" t="n">
+      <c r="F32" s="4" t="n">
         <v>300</v>
       </c>
-      <c r="G22" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" s="4" t="n">
+      <c r="G32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="4" t="n">
         <v>0.3</v>
       </c>
-      <c r="I22" s="4" t="n">
+      <c r="I32" s="4" t="n">
         <v>0.3</v>
       </c>
-      <c r="J22" s="4" t="inlineStr">
+      <c r="J32" s="4" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="K22" s="4" t="inlineStr">
-        <is>
-          <t>Net-zero AI datacenter; Renewable compute</t>
-        </is>
-      </c>
-      <c r="L22" s="4" t="inlineStr">
-        <is>
-          <t>1.5 GW net-zero campus at NEOM Oxagon. First 300 MW by 2028. $5B investment.</t>
+      <c r="K32" s="4" t="inlineStr">
+        <is>
+          <t>Net-zero AI DC; Renewable compute</t>
+        </is>
+      </c>
+      <c r="L32" s="4" t="inlineStr">
+        <is>
+          <t>1.5 GW at NEOM Oxagon. $5B. Net-zero. First 300 MW by 2028.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L22"/>
+  <autoFilter ref="A1:L32"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4273,21 +5336,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:P7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="55" customWidth="1" min="3" max="3"/>
-    <col width="65" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="58" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="55" customWidth="1" min="5" max="5"/>
+    <col width="58" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="85" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="95" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4298,7 +5365,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Mag7 Companies Present</t>
+          <t>Mag7 Present</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -4308,45 +5375,65 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>PE / Financial Sponsors Present</t>
+          <t>SWF / State Entities</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Total Country DC Capacity (MW, est.)</t>
+          <t>Tech / Infra Partners</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>PE / Financial Present</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Country DC Capacity (MW est.)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Mag7 Live (MW)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Mag7 Planned (MW)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>AI Lab Live (MW)</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>AI Lab Planned (MW)</t>
-        </is>
-      </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>SWF/State Live (MW)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>SWF/State Planned (MW)</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Tech Live (MW)</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Tech Planned (MW)</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>PE Live (MW)</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>PE Planned (MW)</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Key Projects &amp; Notes</t>
         </is>
@@ -4365,40 +5452,56 @@
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>OpenAI (Planned — Stargate UAE), Anthropic (Indirect via AWS), xAI (Discussion)</t>
+          <t>OpenAI (Planned — Stargate), Anthropic (Indirect/AWS), xAI (Discussion)</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>KKR/GDH (Live), Silver Lake+MGX/Khazna (Live), SoftBank (Planned), Oracle (Planned)</t>
+          <t>G42/Khazna (Live+Expanding), Mubadala (Indirect), MGX (Live via Khazna)</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
+          <t>Nvidia (Planned), Oracle (Live+Expanding), Cisco (Planned), SoftBank (Planned)</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>KKR/GDH (Live), Silver Lake (Live via Khazna), BlackRock/AIP (Indirect via MGX)</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
           <t>~400</t>
         </is>
       </c>
-      <c r="F2" s="4" t="n">
+      <c r="H2" s="4" t="n">
         <v>230</v>
       </c>
-      <c r="G2" s="4" t="n">
+      <c r="I2" s="4" t="n">
         <v>400</v>
       </c>
-      <c r="H2" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" s="4" t="n">
-        <v>1000</v>
-      </c>
       <c r="J2" s="4" t="n">
+        <v>263</v>
+      </c>
+      <c r="K2" s="4" t="n">
+        <v>937</v>
+      </c>
+      <c r="L2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" s="4" t="n">
+        <v>400</v>
+      </c>
+      <c r="N2" s="4" t="n">
         <v>413</v>
       </c>
-      <c r="K2" s="4" t="n">
-        <v>725</v>
-      </c>
-      <c r="L2" s="4" t="inlineStr">
-        <is>
-          <t>Stargate UAE 5 GW campus (1 GW phase 1, 200 MW in 2026); Microsoft/G42 200 MW expansion; KKR/Gulf Data Hub; Silver Lake+MGX/Khazna 263 MW live</t>
+      <c r="O2" s="4" t="n">
+        <v>525</v>
+      </c>
+      <c r="P2" s="4" t="inlineStr">
+        <is>
+          <t>Stargate UAE 5 GW campus (1 GW ph1, 200 MW Q3 2026); MSFT/G42 200 MW; G42/Khazna 263 MW live; Oracle fivefold expansion; KKR/GDH 7 DCs</t>
         </is>
       </c>
     </row>
@@ -4415,42 +5518,58 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>xAI (Planned — 500 MW with HUMAIN)</t>
+          <t>xAI (Planned — 500 MW HUMAIN)</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>KKR/GDH (Live), Blackstone/AirTrunk (Planned), Silver Lake+MGX/Khazna (Planned), Brookfield/Ori (Planned), DigitalBridge/PIF (Planned), DataVolt/NEOM (Planned)</t>
+          <t>HUMAIN (Planned, 1.9 GW by 2030), G42/Khazna (Planned)</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
+          <t>Nvidia (Planned 500 MW), AMD (Planned 1 GW JV), Oracle (Live), Cisco (Planned 1 GW JV)</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>KKR/GDH (Live), Blackstone/AirTrunk (Planned), Brookfield (Planned), DigitalBridge (Planned), DataVolt (Planned 1.5 GW)</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
           <t>~300</t>
         </is>
       </c>
-      <c r="F3" s="4" t="n">
+      <c r="H3" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="G3" s="4" t="n">
+      <c r="I3" s="4" t="n">
         <v>750</v>
       </c>
-      <c r="H3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" s="4" t="n">
-        <v>500</v>
-      </c>
       <c r="J3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" s="4" t="inlineStr">
-        <is>
-          <t>300+ (disclosed)</t>
-        </is>
-      </c>
-      <c r="L3" s="4" t="inlineStr">
-        <is>
-          <t>HUMAIN ecosystem: 6.6 GW national ambition by 2034; Nvidia 500 MW; xAI 500 MW; AirTrunk $3B; DataVolt/NEOM 1.5 GW; AWS $5.3B region 2026; Microsoft 3-zone region Q4 2026</t>
+        <v>100</v>
+      </c>
+      <c r="K3" s="4" t="n">
+        <v>1800</v>
+      </c>
+      <c r="L3" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="M3" s="4" t="n">
+        <v>2600</v>
+      </c>
+      <c r="N3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" s="4" t="inlineStr">
+        <is>
+          <t>300+</t>
+        </is>
+      </c>
+      <c r="P3" s="4" t="inlineStr">
+        <is>
+          <t>HUMAIN: 6.6 GW by 2034; Nvidia 500 MW; AMD/Cisco/HUMAIN 1 GW JV; xAI 500 MW; AirTrunk $3B; DataVolt/NEOM 1.5 GW; AWS $5.3B; MSFT Q4 2026; Oracle 2 live regions</t>
         </is>
       </c>
     </row>
@@ -4472,33 +5591,49 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>Brookfield ($20B JV with Qai)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>Brookfield ($20B JV w/ Qai)</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
           <t>~50</t>
         </is>
       </c>
-      <c r="F4" s="4" t="n">
+      <c r="H4" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="G4" s="4" t="n">
+      <c r="I4" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="H4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="J4" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="K4" s="4" t="n"/>
-      <c r="L4" s="4" t="inlineStr">
-        <is>
-          <t>Microsoft Azure Qatar Central; Google Cloud Doha region; AWS CloudFront edge; Brookfield-Qai $20B AI infra JV</t>
+      <c r="K4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" s="4" t="n"/>
+      <c r="P4" s="4" t="inlineStr">
+        <is>
+          <t>MSFT Azure Qatar Central; Google Doha; Brookfield-Qai $20B AI JV; AWS CloudFront</t>
         </is>
       </c>
     </row>
@@ -4515,28 +5650,32 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Anthropic (Indirect via AWS Bedrock)</t>
+          <t>Anthropic (Indirect/Bedrock)</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>None announced</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
           <t>~40</t>
         </is>
       </c>
-      <c r="F5" s="4" t="n">
+      <c r="H5" s="4" t="n">
         <v>50</v>
       </c>
-      <c r="G5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="I5" s="4" t="n">
         <v>0</v>
       </c>
@@ -4546,9 +5685,21 @@
       <c r="K5" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L5" s="4" t="inlineStr">
-        <is>
-          <t>AWS first ME region (2019); Claude models available via Bedrock cross-region</t>
+      <c r="L5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" s="4" t="inlineStr">
+        <is>
+          <t>AWS 1st ME region (2019); Claude via Bedrock cross-region</t>
         </is>
       </c>
     </row>
@@ -4570,31 +5721,47 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>KKR/GDH (Planned expansion)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>KKR/GDH (Planned expansion); BlackRock AIP (Kuwait IA is LP)</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
           <t>&lt;10</t>
         </is>
       </c>
-      <c r="F6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="4" t="n"/>
       <c r="H6" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I6" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="I6" s="4" t="n"/>
       <c r="J6" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="K6" s="4" t="n"/>
-      <c r="L6" s="4" t="inlineStr">
-        <is>
-          <t>Microsoft planned Azure region; Google planned third GCC region; GDH expansion planned</t>
+      <c r="K6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" s="4" t="n"/>
+      <c r="P6" s="4" t="inlineStr">
+        <is>
+          <t>MSFT planned Azure region; Google 3rd GCC region; GDH expansion; Kuwait IA is AIP LP</t>
         </is>
       </c>
     </row>
@@ -4616,36 +5783,52 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
           <t>KKR/GDH (Planned expansion)</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>&lt;10</t>
         </is>
       </c>
-      <c r="F7" s="4" t="n"/>
-      <c r="G7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="H7" s="4" t="n"/>
       <c r="I7" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="K7" s="4" t="n"/>
-      <c r="L7" s="4" t="inlineStr">
-        <is>
-          <t>AWS Local Zone + CloudFront edge; GDH expansion planned</t>
+      <c r="K7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" s="4" t="n"/>
+      <c r="P7" s="4" t="inlineStr">
+        <is>
+          <t>AWS Local Zone + CloudFront; GDH expansion planned</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L7"/>
+  <autoFilter ref="A1:P7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4656,50 +5839,50 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="35" customWidth="1" min="6" max="6"/>
-    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="65" customWidth="1" min="5" max="5"/>
+    <col width="38" customWidth="1" min="6" max="6"/>
+    <col width="62" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="18" t="inlineStr">
         <is>
           <t>Partner</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="18" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="18" t="inlineStr">
         <is>
           <t>Capacity (MW)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="18" t="inlineStr">
         <is>
           <t>Investment ($B)</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="18" t="inlineStr">
         <is>
           <t>Key Technology</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="18" t="inlineStr">
         <is>
           <t>Timeline</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="18" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -4723,220 +5906,368 @@
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>18-24 (GPU procurement)</t>
+          <t>18-24 (GPU)</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>18,000 GB300 supercomputers (phase 1); up to 600,000 GPUs over 3 yrs; InfiniBand; Omniverse</t>
+          <t>18K GB300 supercomputers ph1; 600K GPUs over 3 yrs; InfiniBand; Omniverse</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>Q2 2026 (first 100 MW); 500 MW over 5 years</t>
+          <t>Q2 2026 (100 MW); 500 MW / 5 yrs</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
-          <t>Landmark strategic partnership; first chip shipment Dec 2025</t>
+          <t>First chip shipment Dec 2025; $18-24B</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>xAI (Elon Musk)</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>AI Tenant &amp; Developer</t>
+          <t>GPU/CPU Supply &amp; Technology</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="n"/>
+          <t>500 (via $10B deal); 1,000 (via JV)</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>Nvidia GB300 GPUs; Grok model training &amp; deployment</t>
+          <t>Instinct MI450 GPUs; EPYC CPUs; Pensando DPUs; ROCm; Center of Excellence</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>2026-2027 (phased)</t>
+          <t>2026 (100 MW ph1); 1 GW by 2030</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>Framework agreement Nov 2025; Grok to be deployed nationwide in Saudi Arabia</t>
+          <t>$10B May 2025; AMD/Cisco/HUMAIN JV Nov 2025</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Blackstone / AirTrunk</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>DC Developer &amp; Operator</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="n"/>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
+          <t>Infrastructure &amp; JV Partner</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>1,000 (via AMD/Cisco/HUMAIN JV)</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="n"/>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>Hyperscale AI-ready campus; AirTrunk design &amp; build expertise</t>
+          <t>Critical infra; networking; security for GPU clusters</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>2026 (initial phase)</t>
+          <t>2026 (100 MW ph1); 1 GW by 2030</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>AirTrunk's first Middle East project; backed by Blackstone + CPPIB</t>
+          <t>Founding JV investor; exclusive tech partner w/ AMD</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>AWS</t>
+          <t>xAI (Elon Musk)</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="n"/>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>Part of $5.3B Saudi investment</t>
-        </is>
-      </c>
+          <t>AI Tenant &amp; Developer</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="n"/>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>AWS cloud services; SageMaker AI/ML</t>
+          <t>Nvidia GB300 GPUs; Grok model training &amp; deployment</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>2026 (Saudi region launch)</t>
+          <t>2026-27 (phased)</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>Part of broader $23B in US tech deals secured by HUMAIN</t>
+          <t>Framework agreement Nov 2025; Grok nationwide</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Blackstone / AirTrunk</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>AI Chip Supply</t>
+          <t>DC Developer &amp; Operator</t>
         </is>
       </c>
       <c r="C6" s="4" t="n"/>
-      <c r="D6" s="4" t="n"/>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>1,024 Qualcomm Cloud AI 100 accelerators (initial phase)</t>
+          <t>Hyperscale AI-ready campus; AirTrunk expertise</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>Early 2026 (first deployment live)</t>
+          <t>2026 (initial phase)</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>Adobe is pioneer customer on Qualcomm infrastructure</t>
+          <t>AirTrunk's 1st ME project; Blackstone + CPPIB</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Luma AI</t>
+          <t>AWS</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>AI Tenant</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="n"/>
+          <t>Cloud Infra / AI Zone Partner</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>150,000 AI accelerators</t>
+        </is>
+      </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>$0.9 (Series C led by HUMAIN)</t>
+          <t>Part of $5.3B Saudi</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Multimodal AI training on 2 GW Project Halo supercluster</t>
+          <t>AWS cloud; SageMaker; AI Zone in Riyadh</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>2026 (Saudi region)</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>HUMAIN led $900M Series C; a16z, AMD Ventures co-invested</t>
+          <t>HUMAIN preferred global AI partner; $5B+ joint investment</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Total HUMAIN Targets</t>
+          <t>STC / Center3</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
+          <t>JV Partner / DC Operator</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>250 (initial); 1,000 (target)</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="n"/>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>JV: HUMAIN 51%, STC 49%; Center3 DC infrastructure</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>TBD (MOU Dec 2025)</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>1 GW target; HUMAIN majority; STC/Center3 operation</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Qualcomm</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>AI Chip Supply</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="n"/>
+      <c r="D9" s="4" t="n"/>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>1,024 Cloud AI 100 accelerators (initial)</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>Early 2026 (live)</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>Adobe pioneer customer</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Luma AI</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>AI Tenant</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>100 (1st AMD/Cisco JV customer)</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>0.9 (Series C)</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>Multimodal AI training on Project Halo</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>HUMAIN led $900M Series C; a16z co-invested</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>National Infra Fund</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Financing</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>250 (supported by $1.2B)</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>Hyperscale AI DC financing</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>Jan 2026</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>$1.2B framework agreement for 250 MW</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>TOTAL HUMAIN</t>
+        </is>
+      </c>
+      <c r="B12" s="19" t="inlineStr">
+        <is>
           <t>National AI Platform</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C12" s="19" t="inlineStr">
         <is>
           <t>1,900 (by 2030); 6,600 (by 2034)</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>~77 (total infrastructure est.)</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>Multi-vendor GPU infrastructure; sovereign AI capabilities</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>100 MW by Q2 2026 → 1.9 GW by 2030 → 6.6 GW by 2034</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>Targeting 7% of global AI training/inference by 2030; $10B VC fund (Humain Ventures)</t>
+      <c r="D12" s="19" t="inlineStr">
+        <is>
+          <t>~77 (total est.)</t>
+        </is>
+      </c>
+      <c r="E12" s="19" t="inlineStr">
+        <is>
+          <t>Multi-vendor GPU; sovereign AI; multi-exaflop</t>
+        </is>
+      </c>
+      <c r="F12" s="19" t="inlineStr">
+        <is>
+          <t>100 MW Q2 2026 → 1.9 GW by 2030 → 6.6 GW by 2034</t>
+        </is>
+      </c>
+      <c r="G12" s="19" t="inlineStr">
+        <is>
+          <t>7% global AI compute by 2030; $10B VC fund; $23B+ US tech deals secured</t>
         </is>
       </c>
     </row>
@@ -4951,392 +6282,825 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A61"/>
+  <dimension ref="A1:F12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="5" max="5"/>
+    <col width="68" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="20" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="B1" s="20" t="inlineStr">
+        <is>
+          <t>Role</t>
+        </is>
+      </c>
+      <c r="C1" s="20" t="inlineStr">
+        <is>
+          <t>Capacity Exposure (MW)</t>
+        </is>
+      </c>
+      <c r="D1" s="20" t="inlineStr">
+        <is>
+          <t>Key Contribution</t>
+        </is>
+      </c>
+      <c r="E1" s="20" t="inlineStr">
+        <is>
+          <t>Timeline</t>
+        </is>
+      </c>
+      <c r="F1" s="20" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>G42 / Khazna</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>Developer &amp; DC Operator</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>1,000 (ph1); 5,000 (ultimate)</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>Build, own, operate datacenter campus; Khazna DC subsidiary</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>200 MW Q3 2026; 1 GW in ~3 yrs; 5 GW long-term</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>10 sq mi Abu Dhabi campus; Khazna Blackwell-certified; backed by Mubadala, MSFT, Silver Lake</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>AI Platform Operator</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>1,000 (ph1 operator)</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>Operate AI workloads; OpenAI for Countries initiative; GPT model deployment</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Q3 2026 (200 MW); full 1 GW in ~3 yrs</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>First international Stargate; serves ME, Africa, South Asia (~half world's population)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Oracle</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Cloud Operator</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>1,000 (ph1 operator)</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>OCI cloud infrastructure; co-operator with OpenAI</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Q3 2026</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>Also has 2 live UAE regions; fivefold expansion; Blackwell Supercluster</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Nvidia</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>GPU &amp; Technology Partner</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>200 (ph1 chips)</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>~100K GB300 chips ph1; ~1,400 servers; Blackwell architecture</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Q3 2026</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>Also: Khazna Blackwell certification for MEA region</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>SoftBank</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Co-investor / Partner</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>200 (ph1 share)</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Financial backing; strategic partnership; broader $500B Stargate</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Q3 2026</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>Also investing $1B w/ OpenAI in SB Energy for Stargate power</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Cisco</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Preferred Tech Partner</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>N/A (networking/security layer)</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Zero-trust security; AI-ready networking; observability for OpenAI workloads</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Q3 2026</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>Critical infrastructure layer across entire campus</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>MGX</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Strategic Investor (via Khazna)</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Indirect (via Khazna stake)</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>AI infrastructure investment; Khazna minority shareholder</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Ongoing</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>Also: AIP partnership w/ BlackRock, MSFT, NVDA for global DC investing</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Mubadala</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Indirect (via G42 backing)</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Indirect</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Sovereign wealth backing for G42 ecosystem</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Ongoing</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>G42 backer; also backs GlobalFoundries for chip supply chain</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Silver Lake</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Indirect (via Khazna + G42 stakes)</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Indirect</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>PE backing for Khazna and G42</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>Ongoing</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>Khazna minority stake; G42 investor</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Potential Tenants</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Tenants (Under Discussion)</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>AWS, Google, Meta, Microsoft, xAI reportedly in tenant discussions</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>Google and Microsoft reportedly furthest along in negotiations</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>TOTAL STARGATE UAE</t>
+        </is>
+      </c>
+      <c r="B12" s="19" t="inlineStr">
+        <is>
+          <t>AI Infrastructure Campus</t>
+        </is>
+      </c>
+      <c r="C12" s="19" t="inlineStr">
+        <is>
+          <t>Phase 1: 1 GW; Ultimate: 5 GW</t>
+        </is>
+      </c>
+      <c r="D12" s="19" t="inlineStr">
+        <is>
+          <t>Largest AI DC outside US; nuclear/solar/gas power; &gt;$30B total cost</t>
+        </is>
+      </c>
+      <c r="E12" s="19" t="inlineStr">
+        <is>
+          <t>200 MW Q3 2026 → 1 GW ~3 yrs → 5 GW long-term</t>
+        </is>
+      </c>
+      <c r="F12" s="19" t="inlineStr">
+        <is>
+          <t>US-UAE AI Acceleration Partnership; Trump admin rescinded chip export restrictions May 2025</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="13" t="inlineStr">
-        <is>
-          <t>Mag7 + AI Labs + PE/Financial Sponsors — Gulf Datacenter Exposure</t>
+      <c r="A1" s="21" t="inlineStr">
+        <is>
+          <t>Mag7 + AI Labs + SWFs + Tech Partners + PE — Gulf Datacenter Exposure</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="14" t="inlineStr"/>
+      <c r="A2" s="22" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="14" t="inlineStr">
+      <c r="A3" s="22" t="inlineStr">
         <is>
           <t>Data as of: March 2026</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="14" t="inlineStr"/>
+      <c r="A4" s="22" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="inlineStr">
-        <is>
-          <t>ENTITIES COVERED:</t>
+      <c r="A5" s="23" t="inlineStr">
+        <is>
+          <t>ENTITIES COVERED (28 total):</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="14" t="inlineStr"/>
+      <c r="A6" s="22" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
-        <is>
-          <t>Magnificent 7 Companies:</t>
+      <c r="A7" s="23" t="inlineStr">
+        <is>
+          <t>Magnificent 7 (7):</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="14" t="inlineStr">
+      <c r="A8" s="22" t="inlineStr">
         <is>
           <t>Apple, Microsoft, Alphabet (Google), Amazon (AWS), Nvidia, Meta, Tesla</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="14" t="inlineStr"/>
+      <c r="A9" s="22" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
-        <is>
-          <t>AI Labs:</t>
+      <c r="A10" s="23" t="inlineStr">
+        <is>
+          <t>AI Labs (3):</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="14" t="inlineStr">
+      <c r="A11" s="22" t="inlineStr">
         <is>
           <t>OpenAI, Anthropic, xAI (Elon Musk — separate from Tesla)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="14" t="inlineStr"/>
+      <c r="A12" s="22" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="inlineStr">
-        <is>
-          <t>Private Equity &amp; Financial Sponsors:</t>
+      <c r="A13" s="23" t="inlineStr">
+        <is>
+          <t>Sovereign Wealth Funds &amp; State Entities (4):</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="14" t="inlineStr">
-        <is>
-          <t>KKR (via Gulf Data Hub), Blackstone (via AirTrunk), Silver Lake + MGX (via Khazna),</t>
+      <c r="A14" s="22" t="inlineStr">
+        <is>
+          <t>Mubadala (Abu Dhabi SWF), G42 (Abu Dhabi state-backed AI/tech group),</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="14" t="inlineStr">
-        <is>
-          <t>Brookfield (via Qai JV &amp; Ori Industries), DigitalBridge (via PIF partnership),</t>
+      <c r="A15" s="22" t="inlineStr">
+        <is>
+          <t>HUMAIN (Saudi PIF subsidiary — national AI platform), MGX (Abu Dhabi $100B AI fund)</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="14" t="inlineStr">
-        <is>
-          <t>SoftBank (Stargate UAE partner), Oracle (Stargate UAE operator),</t>
-        </is>
-      </c>
+      <c r="A16" s="22" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="14" t="inlineStr">
-        <is>
-          <t>DataVolt / Vision Invest (NEOM Oxagon project)</t>
+      <c r="A17" s="23" t="inlineStr">
+        <is>
+          <t>Technology &amp; Infrastructure Partners (5):</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="14" t="inlineStr"/>
+      <c r="A18" s="22" t="inlineStr">
+        <is>
+          <t>Nvidia, AMD, Oracle, Cisco, SoftBank</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="inlineStr">
-        <is>
-          <t>Gulf States Covered (GCC):</t>
-        </is>
-      </c>
+      <c r="A19" s="22" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="14" t="inlineStr">
+      <c r="A20" s="23" t="inlineStr">
+        <is>
+          <t>Private Equity &amp; Financial Sponsors (7):</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="22" t="inlineStr">
+        <is>
+          <t>KKR (via Gulf Data Hub), Blackstone (via AirTrunk), BlackRock (GIP/AIP with MGX),</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="22" t="inlineStr">
+        <is>
+          <t>Silver Lake (via Khazna/G42), Brookfield (via Qai JV &amp; Ori Industries),</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="22" t="inlineStr">
+        <is>
+          <t>DigitalBridge (via PIF partnership), DataVolt/Vision Invest (NEOM Oxagon)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="22" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="23" t="inlineStr">
+        <is>
+          <t>Gulf States Covered (GCC 6):</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="22" t="inlineStr">
         <is>
           <t>UAE, Saudi Arabia, Qatar, Bahrain, Kuwait, Oman</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="14" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="15" t="inlineStr">
-        <is>
-          <t>CAPACITY ESTIMATES — IMPORTANT CAVEATS:</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="14" t="inlineStr">
-        <is>
-          <t>• Hyperscalers rarely disclose exact MW capacity per facility. Figures are estimates based on public reporting, investment disclosures, and industry analysis.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="14" t="inlineStr">
-        <is>
-          <t>• 'Live Capacity' = operational MW as of early 2026. 'Planned Capacity' = announced expansions and new builds not yet operational.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="14" t="inlineStr">
-        <is>
-          <t>• GW figures are derived by dividing MW by 1,000.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="14" t="inlineStr">
-        <is>
-          <t>• Investment figures may include broader multi-year, multi-country commitments and are not always datacenter-specific.</t>
-        </is>
-      </c>
-    </row>
     <row r="27">
-      <c r="A27" s="14" t="inlineStr">
-        <is>
-          <t>• Country-wide datacenter capacity estimates include all operators, not just entities covered in this analysis.</t>
-        </is>
-      </c>
+      <c r="A27" s="22" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="14" t="inlineStr">
-        <is>
-          <t>• Some entities (e.g., Nvidia, SoftBank, Oracle) participate in the same consortium (Stargate UAE); capacity is not double-counted in country-level summaries.</t>
+      <c r="A28" s="23" t="inlineStr">
+        <is>
+          <t>IMPORTANT NOTES ON OVERLAP:</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="14" t="inlineStr"/>
+      <c r="A29" s="22" t="inlineStr">
+        <is>
+          <t>• Nvidia appears as both Mag7 and Technology partner — capacity NOT double-counted in country summaries</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" s="15" t="inlineStr">
+      <c r="A30" s="22" t="inlineStr">
+        <is>
+          <t>• Stargate UAE partners (OpenAI, Oracle, SoftBank, Nvidia, G42, Cisco) share the same 5 GW campus</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="22" t="inlineStr">
+        <is>
+          <t>• AMD/Cisco/HUMAIN JV: 1 GW capacity shared across AMD, Cisco, and HUMAIN — attributed once</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="22" t="inlineStr">
+        <is>
+          <t>• G42 → Khazna → Stargate UAE; MGX/Silver Lake are Khazna minority investors</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="22" t="inlineStr">
+        <is>
+          <t>• Mubadala is indirect via G42 and MGX; no direct DC ownership</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="22" t="inlineStr">
+        <is>
+          <t>• BlackRock/GIP's Gulf exposure is via AIP partnership with MGX (Abu Dhabi)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="22" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="23" t="inlineStr">
+        <is>
+          <t>CAPACITY ESTIMATES — CAVEATS:</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="22" t="inlineStr">
+        <is>
+          <t>• Hyperscalers rarely disclose exact MW. Figures are estimates from public reporting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="22" t="inlineStr">
+        <is>
+          <t>• 'Live' = operational as of early 2026. 'Planned' = announced but not yet operational.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="22" t="inlineStr">
+        <is>
+          <t>• GW = MW / 1,000.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="22" t="inlineStr">
+        <is>
+          <t>• Investment figures may span multi-year, multi-country commitments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="22" t="inlineStr">
+        <is>
+          <t>• Country-wide MW estimates include all operators, not just entities covered here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="22" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="23" t="inlineStr">
         <is>
           <t>WORKLOAD CATEGORIES:</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="14" t="inlineStr">
-        <is>
-          <t>• Cloud IaaS/PaaS/SaaS: General-purpose cloud computing (VMs, storage, databases, managed services)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="14" t="inlineStr">
-        <is>
-          <t>• AI/ML Training: Large-scale AI model training using GPU clusters</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="14" t="inlineStr">
-        <is>
-          <t>• AI/ML Inference: Running trained AI models for real-time predictions and generation</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="14" t="inlineStr">
-        <is>
-          <t>• Enterprise: Business applications, ERP, CRM, collaboration tools</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="14" t="inlineStr">
-        <is>
-          <t>• Government/Sovereign Cloud: Isolated cloud regions meeting data sovereignty requirements</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="14" t="inlineStr">
-        <is>
-          <t>• Edge Computing: Low-latency content delivery, IoT, and edge workloads</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="14" t="inlineStr">
-        <is>
-          <t>• Colocation/Wholesale: Third-party hosting for enterprise and hyperscale tenants</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="14" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="15" t="inlineStr">
-        <is>
-          <t>KEY DISTINCTIONS:</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="14" t="inlineStr">
-        <is>
-          <t>• Nvidia's role is primarily as GPU/infrastructure supplier and technology partner, not a cloud operator.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="14" t="inlineStr">
-        <is>
-          <t>• Tesla (Mag7) has no direct datacenter exposure. xAI (Elon Musk's separate AI company) is listed under AI Labs.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="14" t="inlineStr">
-        <is>
-          <t>• Anthropic has no owned Gulf infrastructure but Claude models are available via AWS Bedrock cross-region inference in UAE and Bahrain.</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="14" t="inlineStr">
-        <is>
-          <t>• OpenAI's Gulf presence is via the Stargate UAE consortium (with G42, Oracle, SoftBank, Nvidia, Cisco).</t>
-        </is>
-      </c>
-    </row>
     <row r="44">
-      <c r="A44" s="14" t="inlineStr">
-        <is>
-          <t>• Apple has zero datacenter presence or announced plans in any Gulf state.</t>
+      <c r="A44" s="22" t="inlineStr">
+        <is>
+          <t>• Cloud IaaS/PaaS/SaaS: General-purpose cloud computing</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="14" t="inlineStr">
-        <is>
-          <t>• HUMAIN (Saudi PIF subsidiary) is the key local counterparty for multiple entities (Nvidia, xAI, Blackstone/AirTrunk, AWS).</t>
+      <c r="A45" s="22" t="inlineStr">
+        <is>
+          <t>• AI/ML Training: Large-scale model training using GPU clusters</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="14" t="inlineStr">
-        <is>
-          <t>• Stargate UAE participants (OpenAI, Oracle, SoftBank, Nvidia, G42, Cisco) share the same 5 GW campus infrastructure.</t>
+      <c r="A46" s="22" t="inlineStr">
+        <is>
+          <t>• AI/ML Inference: Running trained models for predictions/generation</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="14" t="inlineStr"/>
+      <c r="A47" s="22" t="inlineStr">
+        <is>
+          <t>• Enterprise: Business applications, ERP, CRM</t>
+        </is>
+      </c>
     </row>
     <row r="48">
-      <c r="A48" s="15" t="inlineStr">
-        <is>
-          <t>STATUS COLOR CODING (Project Detail sheet):</t>
+      <c r="A48" s="22" t="inlineStr">
+        <is>
+          <t>• Government/Sovereign Cloud: Isolated regions for data sovereignty</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="14" t="inlineStr">
+      <c r="A49" s="22" t="inlineStr">
+        <is>
+          <t>• Colocation/Wholesale: Third-party hosting</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="22" t="inlineStr">
+        <is>
+          <t>• Edge: Low-latency CDN, IoT</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="22" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="23" t="inlineStr">
+        <is>
+          <t>STATUS COLOR CODING:</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="22" t="inlineStr">
         <is>
           <t>• Green: Live / Operational</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="14" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="22" t="inlineStr">
         <is>
           <t>• Yellow: Planned / Under Construction / Expanding</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="14" t="inlineStr">
-        <is>
-          <t>• Red/Pink: Under Discussion / Not Confirmed</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="14" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="22" t="inlineStr">
+        <is>
+          <t>• Pink: Under Discussion / Not Confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="22" t="inlineStr">
+        <is>
+          <t>• Blue: Indirect (via partner — e.g., Anthropic via AWS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="22" t="inlineStr">
         <is>
           <t>• Grey: No Presence</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="14" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="15" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="22" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="23" t="inlineStr">
         <is>
           <t>SOURCES:</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="14" t="inlineStr">
-        <is>
-          <t>• Reuters, Bloomberg, Forbes, DatacenterDynamics, The National (UAE), Arabian Business</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="14" t="inlineStr">
-        <is>
-          <t>• Microsoft, AWS, Google Cloud official press releases and documentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="14" t="inlineStr">
-        <is>
-          <t>• Nvidia, OpenAI, Anthropic investor relations and press releases</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="14" t="inlineStr">
-        <is>
-          <t>• Blackstone, KKR, Brookfield, Silver Lake, DigitalBridge press releases</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="14" t="inlineStr">
-        <is>
-          <t>• HUMAIN official announcements and Bloomberg/Reuters reporting</t>
-        </is>
-      </c>
-    </row>
     <row r="60">
-      <c r="A60" s="14" t="inlineStr">
+      <c r="A60" s="22" t="inlineStr">
+        <is>
+          <t>• Reuters, Bloomberg, Forbes, DatacenterDynamics, The National (UAE), Arabian Business, AGBI</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="22" t="inlineStr">
+        <is>
+          <t>• Microsoft, AWS, Google Cloud, Oracle, AMD, Nvidia, Cisco official press releases</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="22" t="inlineStr">
+        <is>
+          <t>• OpenAI, Anthropic official announcements</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="22" t="inlineStr">
+        <is>
+          <t>• Blackstone, KKR, Brookfield, Silver Lake, DigitalBridge, BlackRock press releases</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="22" t="inlineStr">
+        <is>
+          <t>• HUMAIN, G42, MGX, Mubadala official announcements</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="22" t="inlineStr">
         <is>
           <t>• GCC Data Center Portfolio Report 2025 (ResearchAndMarkets)</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="14" t="inlineStr">
-        <is>
-          <t>• Middle East Colocation Data Center Market reports (GlobeNewsWire)</t>
+    <row r="66">
+      <c r="A66" s="22" t="inlineStr">
+        <is>
+          <t>• Middle East Colocation DC Market reports (GlobeNewsWire)</t>
         </is>
       </c>
     </row>
